--- a/research/traditional_assets/database/data/uganda/uganda_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_construction_supplies.xlsx
@@ -588,47 +588,53 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0423</v>
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.201</v>
       </c>
       <c r="G2">
-        <v>0.2607626076260762</v>
+        <v>0.2375</v>
       </c>
       <c r="H2">
-        <v>0.2607626076260762</v>
+        <v>0.2375</v>
       </c>
       <c r="I2">
-        <v>0.1389913899138991</v>
+        <v>0.1403846153846154</v>
       </c>
       <c r="J2">
-        <v>0.1142818094847615</v>
+        <v>0.1113096974115931</v>
       </c>
       <c r="K2">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="L2">
-        <v>0.1648216482164822</v>
+        <v>0.1605769230769231</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.08269230769230768</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.2059880239520958</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.08269230769230768</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.2059880239520958</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
         <v>0</v>
       </c>
@@ -636,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1116147965923112</v>
+        <v>0.1838968633370803</v>
       </c>
       <c r="AB2">
-        <v>0.1116147965923112</v>
+        <v>0.1838968633370803</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.503</v>
+        <v>-0.646</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -672,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-2.246520874751491</v>
+        <v>-2.260061919504644</v>
       </c>
     </row>
     <row r="3">
@@ -692,47 +698,53 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0423</v>
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.201</v>
       </c>
       <c r="G3">
-        <v>0.2607626076260762</v>
+        <v>0.2375</v>
       </c>
       <c r="H3">
-        <v>0.2607626076260762</v>
+        <v>0.2375</v>
       </c>
       <c r="I3">
-        <v>0.1389913899138991</v>
+        <v>0.1403846153846154</v>
       </c>
       <c r="J3">
-        <v>0.1142818094847615</v>
+        <v>0.1113096974115931</v>
       </c>
       <c r="K3">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="L3">
-        <v>0.1648216482164822</v>
+        <v>0.1605769230769231</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.344</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.08269230769230768</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2059880239520958</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.344</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.08269230769230768</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2059880239520958</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -740,10 +752,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1116147965923112</v>
+        <v>0.1838968633370803</v>
       </c>
       <c r="AB3">
-        <v>0.1116147965923112</v>
+        <v>0.1838968633370803</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -767,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.503</v>
+        <v>-0.646</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -776,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-2.246520874751491</v>
+        <v>-2.260061919504644</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/uganda/uganda_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_construction_supplies.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ugse_ucl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07099999999999999</v>
+        <v>0.0613</v>
       </c>
       <c r="E2">
-        <v>0.201</v>
+        <v>0.00386</v>
       </c>
       <c r="G2">
-        <v>0.2375</v>
+        <v>0.1708924949290061</v>
       </c>
       <c r="H2">
-        <v>0.2375</v>
+        <v>0.1703853955375254</v>
       </c>
       <c r="I2">
-        <v>0.1403846153846154</v>
+        <v>0.05851926977687626</v>
       </c>
       <c r="J2">
-        <v>0.1113096974115931</v>
+        <v>0.04910237578979273</v>
       </c>
       <c r="K2">
-        <v>1.67</v>
+        <v>0.658</v>
       </c>
       <c r="L2">
-        <v>0.1605769230769231</v>
+        <v>0.0667342799188641</v>
       </c>
       <c r="M2">
-        <v>0.344</v>
+        <v>0.364</v>
       </c>
       <c r="N2">
-        <v>0.08269230769230768</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="O2">
-        <v>0.2059880239520958</v>
+        <v>0.553191489361702</v>
       </c>
       <c r="P2">
-        <v>0.344</v>
+        <v>0.364</v>
       </c>
       <c r="Q2">
-        <v>0.08269230769230768</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="R2">
-        <v>0.2059880239520958</v>
+        <v>0.553191489361702</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -642,10 +644,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1838968633370803</v>
+        <v>0.1292702462339235</v>
       </c>
       <c r="AB2">
-        <v>0.1838968633370803</v>
+        <v>0.1292702462339235</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,19 +668,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM2">
-        <v>-0.646</v>
+        <v>-0.213</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>288.5</v>
+      </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-2.260061919504644</v>
+        <v>-2.708920187793427</v>
       </c>
     </row>
     <row r="3">
@@ -698,46 +703,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07099999999999999</v>
+        <v>0.0613</v>
       </c>
       <c r="E3">
-        <v>0.201</v>
+        <v>0.00386</v>
       </c>
       <c r="G3">
-        <v>0.2375</v>
+        <v>0.1708924949290061</v>
       </c>
       <c r="H3">
-        <v>0.2375</v>
+        <v>0.1703853955375254</v>
       </c>
       <c r="I3">
-        <v>0.1403846153846154</v>
+        <v>0.05851926977687626</v>
       </c>
       <c r="J3">
-        <v>0.1113096974115931</v>
+        <v>0.04910237578979273</v>
       </c>
       <c r="K3">
-        <v>1.67</v>
+        <v>0.658</v>
       </c>
       <c r="L3">
-        <v>0.1605769230769231</v>
+        <v>0.0667342799188641</v>
       </c>
       <c r="M3">
-        <v>0.344</v>
+        <v>0.364</v>
       </c>
       <c r="N3">
-        <v>0.08269230769230768</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="O3">
-        <v>0.2059880239520958</v>
+        <v>0.553191489361702</v>
       </c>
       <c r="P3">
-        <v>0.344</v>
+        <v>0.364</v>
       </c>
       <c r="Q3">
-        <v>0.08269230769230768</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="R3">
-        <v>0.2059880239520958</v>
+        <v>0.553191489361702</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,10 +757,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1838968633370803</v>
+        <v>0.1292702462339235</v>
       </c>
       <c r="AB3">
-        <v>0.1838968633370803</v>
+        <v>0.1292702462339235</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -776,19 +781,8791 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>-0.646</v>
+        <v>-0.213</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>288.5</v>
+      </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-2.260061919504644</v>
+        <v>-2.708920187793427</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Uganda Clays Limited (UGSE:UCL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UGSE:UCL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Construction Supplies</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>288.5</v>
+      </c>
+      <c r="F2">
+        <v>3.50885301250538</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1.74166666666667</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.95</v>
+      </c>
+      <c r="K2">
+        <v>3.08</v>
+      </c>
+      <c r="L2">
+        <v>1.34779855944589</v>
+      </c>
+      <c r="M2">
+        <v>3.08</v>
+      </c>
+      <c r="N2">
+        <v>4.27379855944589</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>2.926</v>
+      </c>
+      <c r="Q2">
+        <v>0.129270246233924</v>
+      </c>
+      <c r="R2">
+        <v>0.103999226057255</v>
+      </c>
+      <c r="S2">
+        <v>0.0775459349119762</v>
+      </c>
+      <c r="T2">
+        <v>0.03934</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.129270246233924</v>
+      </c>
+      <c r="X2">
+        <v>1.33252452114511</v>
+      </c>
+      <c r="Y2">
+        <v>0.715487684377053</v>
+      </c>
+      <c r="Z2">
+        <v>10.2314738865919</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.1107799070171089</v>
+      </c>
+      <c r="AC2">
+        <v>288.5</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0.002</v>
+      </c>
+      <c r="AF2">
+        <v>1.103</v>
+      </c>
+      <c r="AG2">
+        <v>1.68</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>3.08</v>
+      </c>
+      <c r="AK2">
+        <v>0.1264455674211813</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>4.122999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>0.002</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1292702462339235</v>
+      </c>
+      <c r="C2">
+        <v>3.08</v>
+      </c>
+      <c r="D2">
+        <v>3.08</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>3.08</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.68</v>
+      </c>
+      <c r="K2">
+        <v>1.103</v>
+      </c>
+      <c r="L2">
+        <v>0.577</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.577</v>
+      </c>
+      <c r="O2">
+        <v>0.1731</v>
+      </c>
+      <c r="P2">
+        <v>0.4039</v>
+      </c>
+      <c r="Q2">
+        <v>1.5069</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1292702462339235</v>
+      </c>
+      <c r="T2">
+        <v>0.7154876843770529</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03129</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1289237354952218</v>
+      </c>
+      <c r="C3">
+        <v>3.061042086541763</v>
+      </c>
+      <c r="D3">
+        <v>3.091842086541763</v>
+      </c>
+      <c r="E3">
+        <v>0.0308</v>
+      </c>
+      <c r="F3">
+        <v>0.0308</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>3.08</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.68</v>
+      </c>
+      <c r="K3">
+        <v>1.103</v>
+      </c>
+      <c r="L3">
+        <v>0.577</v>
+      </c>
+      <c r="M3">
+        <v>0.00137676</v>
+      </c>
+      <c r="N3">
+        <v>0.57562324</v>
+      </c>
+      <c r="O3">
+        <v>0.172686972</v>
+      </c>
+      <c r="P3">
+        <v>0.402936268</v>
+      </c>
+      <c r="Q3">
+        <v>1.505936268</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1299099348436583</v>
+      </c>
+      <c r="T3">
+        <v>0.7205466882059816</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03129</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>419.099915744211</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.12857722475652</v>
+      </c>
+      <c r="C4">
+        <v>3.042175586249093</v>
+      </c>
+      <c r="D4">
+        <v>3.103775586249093</v>
+      </c>
+      <c r="E4">
+        <v>0.0616</v>
+      </c>
+      <c r="F4">
+        <v>0.0616</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>3.08</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.68</v>
+      </c>
+      <c r="K4">
+        <v>1.103</v>
+      </c>
+      <c r="L4">
+        <v>0.577</v>
+      </c>
+      <c r="M4">
+        <v>0.00275352</v>
+      </c>
+      <c r="N4">
+        <v>0.57424648</v>
+      </c>
+      <c r="O4">
+        <v>0.172273944</v>
+      </c>
+      <c r="P4">
+        <v>0.401972536</v>
+      </c>
+      <c r="Q4">
+        <v>1.504972536</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1305626783229796</v>
+      </c>
+      <c r="T4">
+        <v>0.7257089370110108</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03129</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>209.5499578721055</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1282307140178182</v>
+      </c>
+      <c r="C5">
+        <v>3.023401561697991</v>
+      </c>
+      <c r="D5">
+        <v>3.115801561697991</v>
+      </c>
+      <c r="E5">
+        <v>0.0924</v>
+      </c>
+      <c r="F5">
+        <v>0.0924</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>3.08</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.68</v>
+      </c>
+      <c r="K5">
+        <v>1.103</v>
+      </c>
+      <c r="L5">
+        <v>0.577</v>
+      </c>
+      <c r="M5">
+        <v>0.00413028</v>
+      </c>
+      <c r="N5">
+        <v>0.5728697199999999</v>
+      </c>
+      <c r="O5">
+        <v>0.171860916</v>
+      </c>
+      <c r="P5">
+        <v>0.4010088039999999</v>
+      </c>
+      <c r="Q5">
+        <v>1.504008804</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1312288804307404</v>
+      </c>
+      <c r="T5">
+        <v>0.7309776239357313</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03129</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>139.699971914737</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1278842032791164</v>
+      </c>
+      <c r="C6">
+        <v>3.004721091996863</v>
+      </c>
+      <c r="D6">
+        <v>3.127921091996864</v>
+      </c>
+      <c r="E6">
+        <v>0.1232</v>
+      </c>
+      <c r="F6">
+        <v>0.1232</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>3.08</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.68</v>
+      </c>
+      <c r="K6">
+        <v>1.103</v>
+      </c>
+      <c r="L6">
+        <v>0.577</v>
+      </c>
+      <c r="M6">
+        <v>0.00550704</v>
+      </c>
+      <c r="N6">
+        <v>0.5714929599999999</v>
+      </c>
+      <c r="O6">
+        <v>0.171447888</v>
+      </c>
+      <c r="P6">
+        <v>0.4000450719999999</v>
+      </c>
+      <c r="Q6">
+        <v>1.503045072</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1319089617490796</v>
+      </c>
+      <c r="T6">
+        <v>0.7363560751713836</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03129</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>104.7749789360527</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1275376925404147</v>
+      </c>
+      <c r="C7">
+        <v>2.986135273109304</v>
+      </c>
+      <c r="D7">
+        <v>3.140135273109304</v>
+      </c>
+      <c r="E7">
+        <v>0.154</v>
+      </c>
+      <c r="F7">
+        <v>0.154</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>3.08</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.68</v>
+      </c>
+      <c r="K7">
+        <v>1.103</v>
+      </c>
+      <c r="L7">
+        <v>0.577</v>
+      </c>
+      <c r="M7">
+        <v>0.006883800000000002</v>
+      </c>
+      <c r="N7">
+        <v>0.5701162</v>
+      </c>
+      <c r="O7">
+        <v>0.17103486</v>
+      </c>
+      <c r="P7">
+        <v>0.39908134</v>
+      </c>
+      <c r="Q7">
+        <v>1.50208134</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1326033605688575</v>
+      </c>
+      <c r="T7">
+        <v>0.7418477569593653</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03129</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>83.81998314884218</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1271911818017129</v>
+      </c>
+      <c r="C8">
+        <v>2.967645218184476</v>
+      </c>
+      <c r="D8">
+        <v>3.152445218184476</v>
+      </c>
+      <c r="E8">
+        <v>0.1848</v>
+      </c>
+      <c r="F8">
+        <v>0.1848</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>3.08</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.68</v>
+      </c>
+      <c r="K8">
+        <v>1.103</v>
+      </c>
+      <c r="L8">
+        <v>0.577</v>
+      </c>
+      <c r="M8">
+        <v>0.00826056</v>
+      </c>
+      <c r="N8">
+        <v>0.56873944</v>
+      </c>
+      <c r="O8">
+        <v>0.170621832</v>
+      </c>
+      <c r="P8">
+        <v>0.398117608</v>
+      </c>
+      <c r="Q8">
+        <v>1.501117608</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1333125338316095</v>
+      </c>
+      <c r="T8">
+        <v>0.7474562830407084</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03129</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>69.8499859573685</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1268446710630111</v>
+      </c>
+      <c r="C9">
+        <v>2.949252057895288</v>
+      </c>
+      <c r="D9">
+        <v>3.164852057895288</v>
+      </c>
+      <c r="E9">
+        <v>0.2156</v>
+      </c>
+      <c r="F9">
+        <v>0.2156</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>3.08</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.68</v>
+      </c>
+      <c r="K9">
+        <v>1.103</v>
+      </c>
+      <c r="L9">
+        <v>0.577</v>
+      </c>
+      <c r="M9">
+        <v>0.009637320000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.56736268</v>
+      </c>
+      <c r="O9">
+        <v>0.170208804</v>
+      </c>
+      <c r="P9">
+        <v>0.397153876</v>
+      </c>
+      <c r="Q9">
+        <v>1.500153876</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.13403695813227</v>
+      </c>
+      <c r="T9">
+        <v>0.7531854225861665</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03129</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>59.87141653488729</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1264981603243094</v>
+      </c>
+      <c r="C10">
+        <v>2.930956940784595</v>
+      </c>
+      <c r="D10">
+        <v>3.177356940784595</v>
+      </c>
+      <c r="E10">
+        <v>0.2464</v>
+      </c>
+      <c r="F10">
+        <v>0.2464</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>3.08</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.68</v>
+      </c>
+      <c r="K10">
+        <v>1.103</v>
+      </c>
+      <c r="L10">
+        <v>0.577</v>
+      </c>
+      <c r="M10">
+        <v>0.01101408</v>
+      </c>
+      <c r="N10">
+        <v>0.5659859199999999</v>
+      </c>
+      <c r="O10">
+        <v>0.169795776</v>
+      </c>
+      <c r="P10">
+        <v>0.396190144</v>
+      </c>
+      <c r="Q10">
+        <v>1.499190144</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1347771307872928</v>
+      </c>
+      <c r="T10">
+        <v>0.7590391086434822</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03129</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>52.38748946802637</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1261516495856076</v>
+      </c>
+      <c r="C11">
+        <v>2.912761033619629</v>
+      </c>
+      <c r="D11">
+        <v>3.18996103361963</v>
+      </c>
+      <c r="E11">
+        <v>0.2772</v>
+      </c>
+      <c r="F11">
+        <v>0.2772</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>3.08</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.68</v>
+      </c>
+      <c r="K11">
+        <v>1.103</v>
+      </c>
+      <c r="L11">
+        <v>0.577</v>
+      </c>
+      <c r="M11">
+        <v>0.01239084</v>
+      </c>
+      <c r="N11">
+        <v>0.5646091599999999</v>
+      </c>
+      <c r="O11">
+        <v>0.169382748</v>
+      </c>
+      <c r="P11">
+        <v>0.395226412</v>
+      </c>
+      <c r="Q11">
+        <v>1.498226412</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1355335709731952</v>
+      </c>
+      <c r="T11">
+        <v>0.7650214471416181</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03129</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>46.56665730491233</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1258051388469058</v>
+      </c>
+      <c r="C12">
+        <v>2.894665521754916</v>
+      </c>
+      <c r="D12">
+        <v>3.202665521754916</v>
+      </c>
+      <c r="E12">
+        <v>0.3080000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.3080000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>3.08</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.68</v>
+      </c>
+      <c r="K12">
+        <v>1.103</v>
+      </c>
+      <c r="L12">
+        <v>0.577</v>
+      </c>
+      <c r="M12">
+        <v>0.0137676</v>
+      </c>
+      <c r="N12">
+        <v>0.5632324</v>
+      </c>
+      <c r="O12">
+        <v>0.16896972</v>
+      </c>
+      <c r="P12">
+        <v>0.39426268</v>
+      </c>
+      <c r="Q12">
+        <v>1.49726268</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1363068209410065</v>
+      </c>
+      <c r="T12">
+        <v>0.7711367264952681</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03129</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>41.90999157442109</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1254586281082041</v>
+      </c>
+      <c r="C13">
+        <v>2.876671609503873</v>
+      </c>
+      <c r="D13">
+        <v>3.215471609503873</v>
+      </c>
+      <c r="E13">
+        <v>0.3388</v>
+      </c>
+      <c r="F13">
+        <v>0.3388</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>3.08</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.68</v>
+      </c>
+      <c r="K13">
+        <v>1.103</v>
+      </c>
+      <c r="L13">
+        <v>0.577</v>
+      </c>
+      <c r="M13">
+        <v>0.01514436</v>
+      </c>
+      <c r="N13">
+        <v>0.56185564</v>
+      </c>
+      <c r="O13">
+        <v>0.168556692</v>
+      </c>
+      <c r="P13">
+        <v>0.393298948</v>
+      </c>
+      <c r="Q13">
+        <v>1.496298948</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1370974473125888</v>
+      </c>
+      <c r="T13">
+        <v>0.7773894278568653</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.03129</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>38.09999234038282</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1251121173695023</v>
+      </c>
+      <c r="C14">
+        <v>2.858780520519391</v>
+      </c>
+      <c r="D14">
+        <v>3.228380520519391</v>
+      </c>
+      <c r="E14">
+        <v>0.3696</v>
+      </c>
+      <c r="F14">
+        <v>0.3696</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>3.08</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.68</v>
+      </c>
+      <c r="K14">
+        <v>1.103</v>
+      </c>
+      <c r="L14">
+        <v>0.577</v>
+      </c>
+      <c r="M14">
+        <v>0.01652112</v>
+      </c>
+      <c r="N14">
+        <v>0.56047888</v>
+      </c>
+      <c r="O14">
+        <v>0.168143664</v>
+      </c>
+      <c r="P14">
+        <v>0.392335216</v>
+      </c>
+      <c r="Q14">
+        <v>1.495335216</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1379060424653435</v>
+      </c>
+      <c r="T14">
+        <v>0.7837842360675897</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.03129</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>34.92499297868425</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1247656066308005</v>
+      </c>
+      <c r="C15">
+        <v>2.840993498183585</v>
+      </c>
+      <c r="D15">
+        <v>3.241393498183585</v>
+      </c>
+      <c r="E15">
+        <v>0.4004</v>
+      </c>
+      <c r="F15">
+        <v>0.4004</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>3.08</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.68</v>
+      </c>
+      <c r="K15">
+        <v>1.103</v>
+      </c>
+      <c r="L15">
+        <v>0.577</v>
+      </c>
+      <c r="M15">
+        <v>0.01789788</v>
+      </c>
+      <c r="N15">
+        <v>0.5591021199999999</v>
+      </c>
+      <c r="O15">
+        <v>0.167730636</v>
+      </c>
+      <c r="P15">
+        <v>0.391371484</v>
+      </c>
+      <c r="Q15">
+        <v>1.494371484</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1387332260124144</v>
+      </c>
+      <c r="T15">
+        <v>0.7903260513636182</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03129</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>32.23845505724699</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1244190958920987</v>
+      </c>
+      <c r="C16">
+        <v>2.823311806007043</v>
+      </c>
+      <c r="D16">
+        <v>3.254511806007043</v>
+      </c>
+      <c r="E16">
+        <v>0.4312</v>
+      </c>
+      <c r="F16">
+        <v>0.4312</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>3.08</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.68</v>
+      </c>
+      <c r="K16">
+        <v>1.103</v>
+      </c>
+      <c r="L16">
+        <v>0.577</v>
+      </c>
+      <c r="M16">
+        <v>0.01927464</v>
+      </c>
+      <c r="N16">
+        <v>0.5577253599999999</v>
+      </c>
+      <c r="O16">
+        <v>0.167317608</v>
+      </c>
+      <c r="P16">
+        <v>0.390407752</v>
+      </c>
+      <c r="Q16">
+        <v>1.493407752</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1395796463861613</v>
+      </c>
+      <c r="T16">
+        <v>0.7970200018990892</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.03129</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>29.93570826744364</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1240725851533969</v>
+      </c>
+      <c r="C17">
+        <v>2.805736728037782</v>
+      </c>
+      <c r="D17">
+        <v>3.267736728037781</v>
+      </c>
+      <c r="E17">
+        <v>0.462</v>
+      </c>
+      <c r="F17">
+        <v>0.462</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>3.08</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.68</v>
+      </c>
+      <c r="K17">
+        <v>1.103</v>
+      </c>
+      <c r="L17">
+        <v>0.577</v>
+      </c>
+      <c r="M17">
+        <v>0.0206514</v>
+      </c>
+      <c r="N17">
+        <v>0.5563486</v>
+      </c>
+      <c r="O17">
+        <v>0.16690458</v>
+      </c>
+      <c r="P17">
+        <v>0.38944402</v>
+      </c>
+      <c r="Q17">
+        <v>1.49244402</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1404459825334082</v>
+      </c>
+      <c r="T17">
+        <v>0.8038714571530418</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.03129</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>27.9399943829474</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1237260744146952</v>
+      </c>
+      <c r="C18">
+        <v>2.788269569280227</v>
+      </c>
+      <c r="D18">
+        <v>3.281069569280227</v>
+      </c>
+      <c r="E18">
+        <v>0.4928</v>
+      </c>
+      <c r="F18">
+        <v>0.4928</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>3.08</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.68</v>
+      </c>
+      <c r="K18">
+        <v>1.103</v>
+      </c>
+      <c r="L18">
+        <v>0.577</v>
+      </c>
+      <c r="M18">
+        <v>0.02202816</v>
+      </c>
+      <c r="N18">
+        <v>0.55497184</v>
+      </c>
+      <c r="O18">
+        <v>0.166491552</v>
+      </c>
+      <c r="P18">
+        <v>0.388480288</v>
+      </c>
+      <c r="Q18">
+        <v>1.491480288</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.14133294573178</v>
+      </c>
+      <c r="T18">
+        <v>0.8108860422939933</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.03129</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>26.19374473401319</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1233795636759934</v>
+      </c>
+      <c r="C19">
+        <v>2.770911656124497</v>
+      </c>
+      <c r="D19">
+        <v>3.294511656124497</v>
+      </c>
+      <c r="E19">
+        <v>0.5236000000000001</v>
+      </c>
+      <c r="F19">
+        <v>0.5236000000000001</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>3.08</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.68</v>
+      </c>
+      <c r="K19">
+        <v>1.103</v>
+      </c>
+      <c r="L19">
+        <v>0.577</v>
+      </c>
+      <c r="M19">
+        <v>0.02340492000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.5535950799999999</v>
+      </c>
+      <c r="O19">
+        <v>0.166078524</v>
+      </c>
+      <c r="P19">
+        <v>0.3875165559999999</v>
+      </c>
+      <c r="Q19">
+        <v>1.490516556</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1422412815373415</v>
+      </c>
+      <c r="T19">
+        <v>0.8180696535829196</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03129</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>24.6529362202477</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1230330529372917</v>
+      </c>
+      <c r="C20">
+        <v>2.753664336786269</v>
+      </c>
+      <c r="D20">
+        <v>3.308064336786269</v>
+      </c>
+      <c r="E20">
+        <v>0.5544</v>
+      </c>
+      <c r="F20">
+        <v>0.5544</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>3.08</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.68</v>
+      </c>
+      <c r="K20">
+        <v>1.103</v>
+      </c>
+      <c r="L20">
+        <v>0.577</v>
+      </c>
+      <c r="M20">
+        <v>0.02478168</v>
+      </c>
+      <c r="N20">
+        <v>0.5522183199999999</v>
+      </c>
+      <c r="O20">
+        <v>0.165665496</v>
+      </c>
+      <c r="P20">
+        <v>0.386552824</v>
+      </c>
+      <c r="Q20">
+        <v>1.489552824</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1431717718747459</v>
+      </c>
+      <c r="T20">
+        <v>0.825428474903283</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03129</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>23.28332865245616</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1226865421985899</v>
+      </c>
+      <c r="C21">
+        <v>2.736528981757559</v>
+      </c>
+      <c r="D21">
+        <v>3.321728981757559</v>
+      </c>
+      <c r="E21">
+        <v>0.5852000000000001</v>
+      </c>
+      <c r="F21">
+        <v>0.5852000000000001</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>3.08</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.68</v>
+      </c>
+      <c r="K21">
+        <v>1.103</v>
+      </c>
+      <c r="L21">
+        <v>0.577</v>
+      </c>
+      <c r="M21">
+        <v>0.02615844000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.55084156</v>
+      </c>
+      <c r="O21">
+        <v>0.165252468</v>
+      </c>
+      <c r="P21">
+        <v>0.385589092</v>
+      </c>
+      <c r="Q21">
+        <v>1.488589092</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1441252372822097</v>
+      </c>
+      <c r="T21">
+        <v>0.8329689955155072</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.03129</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>22.05789030232689</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1223400314598881</v>
+      </c>
+      <c r="C22">
+        <v>2.719506984268709</v>
+      </c>
+      <c r="D22">
+        <v>3.335506984268709</v>
+      </c>
+      <c r="E22">
+        <v>0.6160000000000001</v>
+      </c>
+      <c r="F22">
+        <v>0.6160000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>3.08</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.68</v>
+      </c>
+      <c r="K22">
+        <v>1.103</v>
+      </c>
+      <c r="L22">
+        <v>0.577</v>
+      </c>
+      <c r="M22">
+        <v>0.02753520000000001</v>
+      </c>
+      <c r="N22">
+        <v>0.5494648</v>
+      </c>
+      <c r="O22">
+        <v>0.16483944</v>
+      </c>
+      <c r="P22">
+        <v>0.38462536</v>
+      </c>
+      <c r="Q22">
+        <v>1.48762536</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1451025393248601</v>
+      </c>
+      <c r="T22">
+        <v>0.8406980291430372</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.03129</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>20.95499578721055</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1219935207211863</v>
+      </c>
+      <c r="C23">
+        <v>2.702599760761934</v>
+      </c>
+      <c r="D23">
+        <v>3.349399760761933</v>
+      </c>
+      <c r="E23">
+        <v>0.6468</v>
+      </c>
+      <c r="F23">
+        <v>0.6468</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>3.08</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.68</v>
+      </c>
+      <c r="K23">
+        <v>1.103</v>
+      </c>
+      <c r="L23">
+        <v>0.577</v>
+      </c>
+      <c r="M23">
+        <v>0.02891196</v>
+      </c>
+      <c r="N23">
+        <v>0.54808804</v>
+      </c>
+      <c r="O23">
+        <v>0.164426412</v>
+      </c>
+      <c r="P23">
+        <v>0.383661628</v>
+      </c>
+      <c r="Q23">
+        <v>1.486661628</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1461045831913751</v>
+      </c>
+      <c r="T23">
+        <v>0.8486227345079728</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.03129</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>19.95713884496243</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1216470099824846</v>
+      </c>
+      <c r="C24">
+        <v>2.685808751376736</v>
+      </c>
+      <c r="D24">
+        <v>3.363408751376736</v>
+      </c>
+      <c r="E24">
+        <v>0.6776</v>
+      </c>
+      <c r="F24">
+        <v>0.6776</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>3.08</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.68</v>
+      </c>
+      <c r="K24">
+        <v>1.103</v>
+      </c>
+      <c r="L24">
+        <v>0.577</v>
+      </c>
+      <c r="M24">
+        <v>0.03028872</v>
+      </c>
+      <c r="N24">
+        <v>0.5467112799999999</v>
+      </c>
+      <c r="O24">
+        <v>0.164013384</v>
+      </c>
+      <c r="P24">
+        <v>0.3826978959999999</v>
+      </c>
+      <c r="Q24">
+        <v>1.485697896</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1471323204903648</v>
+      </c>
+      <c r="T24">
+        <v>0.8567506374463685</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.03129</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>19.04999617019141</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1213004992437828</v>
+      </c>
+      <c r="C25">
+        <v>2.669135420447572</v>
+      </c>
+      <c r="D25">
+        <v>3.377535420447572</v>
+      </c>
+      <c r="E25">
+        <v>0.7084</v>
+      </c>
+      <c r="F25">
+        <v>0.7084</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>3.08</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.68</v>
+      </c>
+      <c r="K25">
+        <v>1.103</v>
+      </c>
+      <c r="L25">
+        <v>0.577</v>
+      </c>
+      <c r="M25">
+        <v>0.03166548</v>
+      </c>
+      <c r="N25">
+        <v>0.5453345199999999</v>
+      </c>
+      <c r="O25">
+        <v>0.163600356</v>
+      </c>
+      <c r="P25">
+        <v>0.3817341639999999</v>
+      </c>
+      <c r="Q25">
+        <v>1.484734164</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.148186752264653</v>
+      </c>
+      <c r="T25">
+        <v>0.8650896547468002</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.03129</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>18.22173546713961</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.120953988505081</v>
+      </c>
+      <c r="C26">
+        <v>2.652581257014085</v>
+      </c>
+      <c r="D26">
+        <v>3.391781257014085</v>
+      </c>
+      <c r="E26">
+        <v>0.7392</v>
+      </c>
+      <c r="F26">
+        <v>0.7392</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>3.08</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.68</v>
+      </c>
+      <c r="K26">
+        <v>1.103</v>
+      </c>
+      <c r="L26">
+        <v>0.577</v>
+      </c>
+      <c r="M26">
+        <v>0.03304224</v>
+      </c>
+      <c r="N26">
+        <v>0.54395776</v>
+      </c>
+      <c r="O26">
+        <v>0.163187328</v>
+      </c>
+      <c r="P26">
+        <v>0.3807704319999999</v>
+      </c>
+      <c r="Q26">
+        <v>1.483770432</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1492689322435277</v>
+      </c>
+      <c r="T26">
+        <v>0.8736481198709277</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.03129</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>17.46249648934213</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1206074777663793</v>
+      </c>
+      <c r="C27">
+        <v>2.636147775344341</v>
+      </c>
+      <c r="D27">
+        <v>3.406147775344341</v>
+      </c>
+      <c r="E27">
+        <v>0.77</v>
+      </c>
+      <c r="F27">
+        <v>0.77</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>3.08</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.68</v>
+      </c>
+      <c r="K27">
+        <v>1.103</v>
+      </c>
+      <c r="L27">
+        <v>0.577</v>
+      </c>
+      <c r="M27">
+        <v>0.03441900000000001</v>
+      </c>
+      <c r="N27">
+        <v>0.542581</v>
+      </c>
+      <c r="O27">
+        <v>0.1627743</v>
+      </c>
+      <c r="P27">
+        <v>0.3798067</v>
+      </c>
+      <c r="Q27">
+        <v>1.4828067</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1503799703551724</v>
+      </c>
+      <c r="T27">
+        <v>0.8824348107316986</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.03129</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>16.76399662976844</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1202609670276775</v>
+      </c>
+      <c r="C28">
+        <v>2.619836515471389</v>
+      </c>
+      <c r="D28">
+        <v>3.42063651547139</v>
+      </c>
+      <c r="E28">
+        <v>0.8008000000000001</v>
+      </c>
+      <c r="F28">
+        <v>0.8008000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>3.08</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.68</v>
+      </c>
+      <c r="K28">
+        <v>1.103</v>
+      </c>
+      <c r="L28">
+        <v>0.577</v>
+      </c>
+      <c r="M28">
+        <v>0.03579576</v>
+      </c>
+      <c r="N28">
+        <v>0.54120424</v>
+      </c>
+      <c r="O28">
+        <v>0.162361272</v>
+      </c>
+      <c r="P28">
+        <v>0.378842968</v>
+      </c>
+      <c r="Q28">
+        <v>1.481842968</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1515210365238885</v>
+      </c>
+      <c r="T28">
+        <v>0.8914589797238416</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.03129</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>16.1192275286235</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1199144562889757</v>
+      </c>
+      <c r="C29">
+        <v>2.603649043743582</v>
+      </c>
+      <c r="D29">
+        <v>3.435249043743582</v>
+      </c>
+      <c r="E29">
+        <v>0.8316000000000001</v>
+      </c>
+      <c r="F29">
+        <v>0.8316000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>3.08</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.68</v>
+      </c>
+      <c r="K29">
+        <v>1.103</v>
+      </c>
+      <c r="L29">
+        <v>0.577</v>
+      </c>
+      <c r="M29">
+        <v>0.03717252000000001</v>
+      </c>
+      <c r="N29">
+        <v>0.5398274799999999</v>
+      </c>
+      <c r="O29">
+        <v>0.161948244</v>
+      </c>
+      <c r="P29">
+        <v>0.377879236</v>
+      </c>
+      <c r="Q29">
+        <v>1.480879236</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1526933647794188</v>
+      </c>
+      <c r="T29">
+        <v>0.9007303862226187</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.03129</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>15.52221910163744</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1195679455502739</v>
+      </c>
+      <c r="C30">
+        <v>2.587586953389078</v>
+      </c>
+      <c r="D30">
+        <v>3.449986953389078</v>
+      </c>
+      <c r="E30">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="F30">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>3.08</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.68</v>
+      </c>
+      <c r="K30">
+        <v>1.103</v>
+      </c>
+      <c r="L30">
+        <v>0.577</v>
+      </c>
+      <c r="M30">
+        <v>0.03854928000000001</v>
+      </c>
+      <c r="N30">
+        <v>0.5384507199999999</v>
+      </c>
+      <c r="O30">
+        <v>0.161535216</v>
+      </c>
+      <c r="P30">
+        <v>0.376915504</v>
+      </c>
+      <c r="Q30">
+        <v>1.479915504</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1538982577087138</v>
+      </c>
+      <c r="T30">
+        <v>0.9102593317908061</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.03129</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>14.96785413372182</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1192214348115722</v>
+      </c>
+      <c r="C31">
+        <v>2.571651865094909</v>
+      </c>
+      <c r="D31">
+        <v>3.464851865094909</v>
+      </c>
+      <c r="E31">
+        <v>0.8932</v>
+      </c>
+      <c r="F31">
+        <v>0.8932</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>3.08</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.68</v>
+      </c>
+      <c r="K31">
+        <v>1.103</v>
+      </c>
+      <c r="L31">
+        <v>0.577</v>
+      </c>
+      <c r="M31">
+        <v>0.03992604</v>
+      </c>
+      <c r="N31">
+        <v>0.53707396</v>
+      </c>
+      <c r="O31">
+        <v>0.161122188</v>
+      </c>
+      <c r="P31">
+        <v>0.375951772</v>
+      </c>
+      <c r="Q31">
+        <v>1.478951772</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1551370912839045</v>
+      </c>
+      <c r="T31">
+        <v>0.9200566983609145</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.03129</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>14.451721232559</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1188749240728704</v>
+      </c>
+      <c r="C32">
+        <v>2.555845427601115</v>
+      </c>
+      <c r="D32">
+        <v>3.479845427601115</v>
+      </c>
+      <c r="E32">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="F32">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>3.08</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.68</v>
+      </c>
+      <c r="K32">
+        <v>1.103</v>
+      </c>
+      <c r="L32">
+        <v>0.577</v>
+      </c>
+      <c r="M32">
+        <v>0.0413028</v>
+      </c>
+      <c r="N32">
+        <v>0.5356972</v>
+      </c>
+      <c r="O32">
+        <v>0.16070916</v>
+      </c>
+      <c r="P32">
+        <v>0.37498804</v>
+      </c>
+      <c r="Q32">
+        <v>1.47798804</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1564113201041006</v>
+      </c>
+      <c r="T32">
+        <v>0.9301339896901688</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.03129</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>13.9699971914737</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1185284133341686</v>
+      </c>
+      <c r="C33">
+        <v>2.540169318310342</v>
+      </c>
+      <c r="D33">
+        <v>3.494969318310342</v>
+      </c>
+      <c r="E33">
+        <v>0.9548</v>
+      </c>
+      <c r="F33">
+        <v>0.9548</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>3.08</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.68</v>
+      </c>
+      <c r="K33">
+        <v>1.103</v>
+      </c>
+      <c r="L33">
+        <v>0.577</v>
+      </c>
+      <c r="M33">
+        <v>0.04267956000000001</v>
+      </c>
+      <c r="N33">
+        <v>0.5343204399999999</v>
+      </c>
+      <c r="O33">
+        <v>0.160296132</v>
+      </c>
+      <c r="P33">
+        <v>0.374024308</v>
+      </c>
+      <c r="Q33">
+        <v>1.477024308</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.157722483092998</v>
+      </c>
+      <c r="T33">
+        <v>0.9405033764202709</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.3</v>
+      </c>
+      <c r="W33">
+        <v>0.03129</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>13.519352120781</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1181819025954669</v>
+      </c>
+      <c r="C34">
+        <v>2.524625243913426</v>
+      </c>
+      <c r="D34">
+        <v>3.510225243913426</v>
+      </c>
+      <c r="E34">
+        <v>0.9856</v>
+      </c>
+      <c r="F34">
+        <v>0.9856</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>3.08</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.68</v>
+      </c>
+      <c r="K34">
+        <v>1.103</v>
+      </c>
+      <c r="L34">
+        <v>0.577</v>
+      </c>
+      <c r="M34">
+        <v>0.04405632</v>
+      </c>
+      <c r="N34">
+        <v>0.5329436799999999</v>
+      </c>
+      <c r="O34">
+        <v>0.159883104</v>
+      </c>
+      <c r="P34">
+        <v>0.373060576</v>
+      </c>
+      <c r="Q34">
+        <v>1.476060576</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.159072209699216</v>
+      </c>
+      <c r="T34">
+        <v>0.9511777451130232</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.3</v>
+      </c>
+      <c r="W34">
+        <v>0.03129</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>13.09687236700659</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1180894918567651</v>
+      </c>
+      <c r="C35">
+        <v>2.497916359901224</v>
+      </c>
+      <c r="D35">
+        <v>3.514316359901224</v>
+      </c>
+      <c r="E35">
+        <v>1.0164</v>
+      </c>
+      <c r="F35">
+        <v>1.0164</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>3.08</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.68</v>
+      </c>
+      <c r="K35">
+        <v>1.103</v>
+      </c>
+      <c r="L35">
+        <v>0.577</v>
+      </c>
+      <c r="M35">
+        <v>0.04655112</v>
+      </c>
+      <c r="N35">
+        <v>0.53044888</v>
+      </c>
+      <c r="O35">
+        <v>0.159134664</v>
+      </c>
+      <c r="P35">
+        <v>0.371314216</v>
+      </c>
+      <c r="Q35">
+        <v>1.474314216</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1604622266518882</v>
+      </c>
+      <c r="T35">
+        <v>0.9621707516772011</v>
+      </c>
+      <c r="U35">
+        <v>0.0458</v>
+      </c>
+      <c r="V35">
+        <v>0.3</v>
+      </c>
+      <c r="W35">
+        <v>0.03206</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>12.39497567405467</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1177506811180633</v>
+      </c>
+      <c r="C36">
+        <v>2.482197776616924</v>
+      </c>
+      <c r="D36">
+        <v>3.529397776616924</v>
+      </c>
+      <c r="E36">
+        <v>1.0472</v>
+      </c>
+      <c r="F36">
+        <v>1.0472</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>3.08</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.68</v>
+      </c>
+      <c r="K36">
+        <v>1.103</v>
+      </c>
+      <c r="L36">
+        <v>0.577</v>
+      </c>
+      <c r="M36">
+        <v>0.04796176000000001</v>
+      </c>
+      <c r="N36">
+        <v>0.52903824</v>
+      </c>
+      <c r="O36">
+        <v>0.158711472</v>
+      </c>
+      <c r="P36">
+        <v>0.370326768</v>
+      </c>
+      <c r="Q36">
+        <v>1.473326768</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.161894365330399</v>
+      </c>
+      <c r="T36">
+        <v>0.9734968796524144</v>
+      </c>
+      <c r="U36">
+        <v>0.0458</v>
+      </c>
+      <c r="V36">
+        <v>0.3</v>
+      </c>
+      <c r="W36">
+        <v>0.03206</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>12.03041756599424</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1174118703793615</v>
+      </c>
+      <c r="C37">
+        <v>2.466609192680393</v>
+      </c>
+      <c r="D37">
+        <v>3.544609192680394</v>
+      </c>
+      <c r="E37">
+        <v>1.078</v>
+      </c>
+      <c r="F37">
+        <v>1.078</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>3.08</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.68</v>
+      </c>
+      <c r="K37">
+        <v>1.103</v>
+      </c>
+      <c r="L37">
+        <v>0.577</v>
+      </c>
+      <c r="M37">
+        <v>0.0493724</v>
+      </c>
+      <c r="N37">
+        <v>0.5276276</v>
+      </c>
+      <c r="O37">
+        <v>0.15828828</v>
+      </c>
+      <c r="P37">
+        <v>0.36933932</v>
+      </c>
+      <c r="Q37">
+        <v>1.47233932</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1633705698144024</v>
+      </c>
+      <c r="T37">
+        <v>0.985171503873019</v>
+      </c>
+      <c r="U37">
+        <v>0.0458</v>
+      </c>
+      <c r="V37">
+        <v>0.3</v>
+      </c>
+      <c r="W37">
+        <v>0.03206</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>11.68669134982298</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1170730596406598</v>
+      </c>
+      <c r="C38">
+        <v>2.451152296227061</v>
+      </c>
+      <c r="D38">
+        <v>3.559952296227061</v>
+      </c>
+      <c r="E38">
+        <v>1.1088</v>
+      </c>
+      <c r="F38">
+        <v>1.1088</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>3.08</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.68</v>
+      </c>
+      <c r="K38">
+        <v>1.103</v>
+      </c>
+      <c r="L38">
+        <v>0.577</v>
+      </c>
+      <c r="M38">
+        <v>0.05078304</v>
+      </c>
+      <c r="N38">
+        <v>0.52621696</v>
+      </c>
+      <c r="O38">
+        <v>0.157865088</v>
+      </c>
+      <c r="P38">
+        <v>0.368351872</v>
+      </c>
+      <c r="Q38">
+        <v>1.471351872</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1648929056885309</v>
+      </c>
+      <c r="T38">
+        <v>0.9972109601005175</v>
+      </c>
+      <c r="U38">
+        <v>0.0458</v>
+      </c>
+      <c r="V38">
+        <v>0.3</v>
+      </c>
+      <c r="W38">
+        <v>0.03206</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>11.36206103455012</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.116734248901958</v>
+      </c>
+      <c r="C39">
+        <v>2.435828804748303</v>
+      </c>
+      <c r="D39">
+        <v>3.575428804748303</v>
+      </c>
+      <c r="E39">
+        <v>1.1396</v>
+      </c>
+      <c r="F39">
+        <v>1.1396</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>3.08</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.68</v>
+      </c>
+      <c r="K39">
+        <v>1.103</v>
+      </c>
+      <c r="L39">
+        <v>0.577</v>
+      </c>
+      <c r="M39">
+        <v>0.05219368</v>
+      </c>
+      <c r="N39">
+        <v>0.5248063199999999</v>
+      </c>
+      <c r="O39">
+        <v>0.157441896</v>
+      </c>
+      <c r="P39">
+        <v>0.367364424</v>
+      </c>
+      <c r="Q39">
+        <v>1.470364424</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1664635696856476</v>
+      </c>
+      <c r="T39">
+        <v>1.009632621287619</v>
+      </c>
+      <c r="U39">
+        <v>0.0458</v>
+      </c>
+      <c r="V39">
+        <v>0.3</v>
+      </c>
+      <c r="W39">
+        <v>0.03206</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>11.0549783038866</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1163954381632562</v>
+      </c>
+      <c r="C40">
+        <v>2.420640465732338</v>
+      </c>
+      <c r="D40">
+        <v>3.591040465732338</v>
+      </c>
+      <c r="E40">
+        <v>1.1704</v>
+      </c>
+      <c r="F40">
+        <v>1.1704</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>3.08</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.68</v>
+      </c>
+      <c r="K40">
+        <v>1.103</v>
+      </c>
+      <c r="L40">
+        <v>0.577</v>
+      </c>
+      <c r="M40">
+        <v>0.05360432</v>
+      </c>
+      <c r="N40">
+        <v>0.5233956799999999</v>
+      </c>
+      <c r="O40">
+        <v>0.157018704</v>
+      </c>
+      <c r="P40">
+        <v>0.366376976</v>
+      </c>
+      <c r="Q40">
+        <v>1.469376976</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1680849002633165</v>
+      </c>
+      <c r="T40">
+        <v>1.022454981222692</v>
+      </c>
+      <c r="U40">
+        <v>0.0458</v>
+      </c>
+      <c r="V40">
+        <v>0.3</v>
+      </c>
+      <c r="W40">
+        <v>0.03206</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>10.76405782220537</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1160566274245545</v>
+      </c>
+      <c r="C41">
+        <v>2.405589057321982</v>
+      </c>
+      <c r="D41">
+        <v>3.606789057321982</v>
+      </c>
+      <c r="E41">
+        <v>1.2012</v>
+      </c>
+      <c r="F41">
+        <v>1.2012</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>3.08</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.68</v>
+      </c>
+      <c r="K41">
+        <v>1.103</v>
+      </c>
+      <c r="L41">
+        <v>0.577</v>
+      </c>
+      <c r="M41">
+        <v>0.05501496</v>
+      </c>
+      <c r="N41">
+        <v>0.5219850399999999</v>
+      </c>
+      <c r="O41">
+        <v>0.156595512</v>
+      </c>
+      <c r="P41">
+        <v>0.3653895279999999</v>
+      </c>
+      <c r="Q41">
+        <v>1.468389528</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1697593892205811</v>
+      </c>
+      <c r="T41">
+        <v>1.035697746401537</v>
+      </c>
+      <c r="U41">
+        <v>0.0458</v>
+      </c>
+      <c r="V41">
+        <v>0.3</v>
+      </c>
+      <c r="W41">
+        <v>0.03206</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>10.48805633958472</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1157178166858527</v>
+      </c>
+      <c r="C42">
+        <v>2.390676388989802</v>
+      </c>
+      <c r="D42">
+        <v>3.622676388989802</v>
+      </c>
+      <c r="E42">
+        <v>1.232</v>
+      </c>
+      <c r="F42">
+        <v>1.232</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>3.08</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.68</v>
+      </c>
+      <c r="K42">
+        <v>1.103</v>
+      </c>
+      <c r="L42">
+        <v>0.577</v>
+      </c>
+      <c r="M42">
+        <v>0.05642560000000001</v>
+      </c>
+      <c r="N42">
+        <v>0.5205744</v>
+      </c>
+      <c r="O42">
+        <v>0.15617232</v>
+      </c>
+      <c r="P42">
+        <v>0.36440208</v>
+      </c>
+      <c r="Q42">
+        <v>1.46740208</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1714896944764212</v>
+      </c>
+      <c r="T42">
+        <v>1.049381937086344</v>
+      </c>
+      <c r="U42">
+        <v>0.0458</v>
+      </c>
+      <c r="V42">
+        <v>0.3</v>
+      </c>
+      <c r="W42">
+        <v>0.03206</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>10.2258549310951</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1153790059471509</v>
+      </c>
+      <c r="C43">
+        <v>2.37590430223117</v>
+      </c>
+      <c r="D43">
+        <v>3.63870430223117</v>
+      </c>
+      <c r="E43">
+        <v>1.2628</v>
+      </c>
+      <c r="F43">
+        <v>1.2628</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>3.08</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.68</v>
+      </c>
+      <c r="K43">
+        <v>1.103</v>
+      </c>
+      <c r="L43">
+        <v>0.577</v>
+      </c>
+      <c r="M43">
+        <v>0.05783624</v>
+      </c>
+      <c r="N43">
+        <v>0.51916376</v>
+      </c>
+      <c r="O43">
+        <v>0.155749128</v>
+      </c>
+      <c r="P43">
+        <v>0.363414632</v>
+      </c>
+      <c r="Q43">
+        <v>1.466414632</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1732786541477135</v>
+      </c>
+      <c r="T43">
+        <v>1.063529998641823</v>
+      </c>
+      <c r="U43">
+        <v>0.0458</v>
+      </c>
+      <c r="V43">
+        <v>0.3</v>
+      </c>
+      <c r="W43">
+        <v>0.03206</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>9.976443835214736</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1156869952084492</v>
+      </c>
+      <c r="C44">
+        <v>2.330528601267846</v>
+      </c>
+      <c r="D44">
+        <v>3.624128601267846</v>
+      </c>
+      <c r="E44">
+        <v>1.2936</v>
+      </c>
+      <c r="F44">
+        <v>1.2936</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>3.08</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.68</v>
+      </c>
+      <c r="K44">
+        <v>1.103</v>
+      </c>
+      <c r="L44">
+        <v>0.577</v>
+      </c>
+      <c r="M44">
+        <v>0.0620928</v>
+      </c>
+      <c r="N44">
+        <v>0.5149071999999999</v>
+      </c>
+      <c r="O44">
+        <v>0.15447216</v>
+      </c>
+      <c r="P44">
+        <v>0.3604350399999999</v>
+      </c>
+      <c r="Q44">
+        <v>1.46343504</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.175129302083533</v>
+      </c>
+      <c r="T44">
+        <v>1.078165924388869</v>
+      </c>
+      <c r="U44">
+        <v>0.048</v>
+      </c>
+      <c r="V44">
+        <v>0.3</v>
+      </c>
+      <c r="W44">
+        <v>0.0336</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>9.29254277468563</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1153635844697474</v>
+      </c>
+      <c r="C45">
+        <v>2.315037211963175</v>
+      </c>
+      <c r="D45">
+        <v>3.639437211963175</v>
+      </c>
+      <c r="E45">
+        <v>1.3244</v>
+      </c>
+      <c r="F45">
+        <v>1.3244</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>3.08</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.68</v>
+      </c>
+      <c r="K45">
+        <v>1.103</v>
+      </c>
+      <c r="L45">
+        <v>0.577</v>
+      </c>
+      <c r="M45">
+        <v>0.06357120000000001</v>
+      </c>
+      <c r="N45">
+        <v>0.5134287999999999</v>
+      </c>
+      <c r="O45">
+        <v>0.15402864</v>
+      </c>
+      <c r="P45">
+        <v>0.35940016</v>
+      </c>
+      <c r="Q45">
+        <v>1.46240016</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1770448850346445</v>
+      </c>
+      <c r="T45">
+        <v>1.093315391390198</v>
+      </c>
+      <c r="U45">
+        <v>0.048</v>
+      </c>
+      <c r="V45">
+        <v>0.3</v>
+      </c>
+      <c r="W45">
+        <v>0.0336</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>9.076437128762707</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1150401737310456</v>
+      </c>
+      <c r="C46">
+        <v>2.299675700880211</v>
+      </c>
+      <c r="D46">
+        <v>3.654875700880211</v>
+      </c>
+      <c r="E46">
+        <v>1.3552</v>
+      </c>
+      <c r="F46">
+        <v>1.3552</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>3.08</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.68</v>
+      </c>
+      <c r="K46">
+        <v>1.103</v>
+      </c>
+      <c r="L46">
+        <v>0.577</v>
+      </c>
+      <c r="M46">
+        <v>0.0650496</v>
+      </c>
+      <c r="N46">
+        <v>0.5119503999999999</v>
+      </c>
+      <c r="O46">
+        <v>0.15358512</v>
+      </c>
+      <c r="P46">
+        <v>0.35836528</v>
+      </c>
+      <c r="Q46">
+        <v>1.46136528</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1790288816625815</v>
+      </c>
+      <c r="T46">
+        <v>1.109005910784432</v>
+      </c>
+      <c r="U46">
+        <v>0.048</v>
+      </c>
+      <c r="V46">
+        <v>0.3</v>
+      </c>
+      <c r="W46">
+        <v>0.0336</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.870154466745374</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1147167629923439</v>
+      </c>
+      <c r="C47">
+        <v>2.284445727889977</v>
+      </c>
+      <c r="D47">
+        <v>3.670445727889978</v>
+      </c>
+      <c r="E47">
+        <v>1.386</v>
+      </c>
+      <c r="F47">
+        <v>1.386</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>3.08</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.68</v>
+      </c>
+      <c r="K47">
+        <v>1.103</v>
+      </c>
+      <c r="L47">
+        <v>0.577</v>
+      </c>
+      <c r="M47">
+        <v>0.066528</v>
+      </c>
+      <c r="N47">
+        <v>0.5104719999999999</v>
+      </c>
+      <c r="O47">
+        <v>0.1531416</v>
+      </c>
+      <c r="P47">
+        <v>0.3573303999999999</v>
+      </c>
+      <c r="Q47">
+        <v>1.4603304</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1810850236224434</v>
+      </c>
+      <c r="T47">
+        <v>1.125266994520274</v>
+      </c>
+      <c r="U47">
+        <v>0.048</v>
+      </c>
+      <c r="V47">
+        <v>0.3</v>
+      </c>
+      <c r="W47">
+        <v>0.0336</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>8.673039923039921</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1143933522536421</v>
+      </c>
+      <c r="C48">
+        <v>2.269348981269173</v>
+      </c>
+      <c r="D48">
+        <v>3.686148981269172</v>
+      </c>
+      <c r="E48">
+        <v>1.4168</v>
+      </c>
+      <c r="F48">
+        <v>1.4168</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>3.08</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.68</v>
+      </c>
+      <c r="K48">
+        <v>1.103</v>
+      </c>
+      <c r="L48">
+        <v>0.577</v>
+      </c>
+      <c r="M48">
+        <v>0.06800640000000001</v>
+      </c>
+      <c r="N48">
+        <v>0.5089935999999999</v>
+      </c>
+      <c r="O48">
+        <v>0.15269808</v>
+      </c>
+      <c r="P48">
+        <v>0.35629552</v>
+      </c>
+      <c r="Q48">
+        <v>1.45929552</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1832173189882261</v>
+      </c>
+      <c r="T48">
+        <v>1.142130340616703</v>
+      </c>
+      <c r="U48">
+        <v>0.048</v>
+      </c>
+      <c r="V48">
+        <v>0.3</v>
+      </c>
+      <c r="W48">
+        <v>0.0336</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>8.484495576886879</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1140699415149403</v>
+      </c>
+      <c r="C49">
+        <v>2.254387178310423</v>
+      </c>
+      <c r="D49">
+        <v>3.701987178310423</v>
+      </c>
+      <c r="E49">
+        <v>1.4476</v>
+      </c>
+      <c r="F49">
+        <v>1.4476</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>3.08</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.68</v>
+      </c>
+      <c r="K49">
+        <v>1.103</v>
+      </c>
+      <c r="L49">
+        <v>0.577</v>
+      </c>
+      <c r="M49">
+        <v>0.06948480000000001</v>
+      </c>
+      <c r="N49">
+        <v>0.5075151999999999</v>
+      </c>
+      <c r="O49">
+        <v>0.15225456</v>
+      </c>
+      <c r="P49">
+        <v>0.35526064</v>
+      </c>
+      <c r="Q49">
+        <v>1.45826064</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.185430078330076</v>
+      </c>
+      <c r="T49">
+        <v>1.159630039396016</v>
+      </c>
+      <c r="U49">
+        <v>0.048</v>
+      </c>
+      <c r="V49">
+        <v>0.3</v>
+      </c>
+      <c r="W49">
+        <v>0.0336</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>8.303974394399924</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1137465307762385</v>
+      </c>
+      <c r="C50">
+        <v>2.239562065948337</v>
+      </c>
+      <c r="D50">
+        <v>3.717962065948337</v>
+      </c>
+      <c r="E50">
+        <v>1.4784</v>
+      </c>
+      <c r="F50">
+        <v>1.4784</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>3.08</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.68</v>
+      </c>
+      <c r="K50">
+        <v>1.103</v>
+      </c>
+      <c r="L50">
+        <v>0.577</v>
+      </c>
+      <c r="M50">
+        <v>0.0709632</v>
+      </c>
+      <c r="N50">
+        <v>0.5060368</v>
+      </c>
+      <c r="O50">
+        <v>0.15181104</v>
+      </c>
+      <c r="P50">
+        <v>0.3542257599999999</v>
+      </c>
+      <c r="Q50">
+        <v>1.45722576</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1877279438004587</v>
+      </c>
+      <c r="T50">
+        <v>1.177802803512995</v>
+      </c>
+      <c r="U50">
+        <v>0.048</v>
+      </c>
+      <c r="V50">
+        <v>0.3</v>
+      </c>
+      <c r="W50">
+        <v>0.0336</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>8.130974927849927</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1134231200375368</v>
+      </c>
+      <c r="C51">
+        <v>2.22487542140183</v>
+      </c>
+      <c r="D51">
+        <v>3.73407542140183</v>
+      </c>
+      <c r="E51">
+        <v>1.5092</v>
+      </c>
+      <c r="F51">
+        <v>1.5092</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>3.08</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.68</v>
+      </c>
+      <c r="K51">
+        <v>1.103</v>
+      </c>
+      <c r="L51">
+        <v>0.577</v>
+      </c>
+      <c r="M51">
+        <v>0.07244160000000001</v>
+      </c>
+      <c r="N51">
+        <v>0.5045584</v>
+      </c>
+      <c r="O51">
+        <v>0.15136752</v>
+      </c>
+      <c r="P51">
+        <v>0.35319088</v>
+      </c>
+      <c r="Q51">
+        <v>1.45619088</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1901159216422289</v>
+      </c>
+      <c r="T51">
+        <v>1.196688225046326</v>
+      </c>
+      <c r="U51">
+        <v>0.048</v>
+      </c>
+      <c r="V51">
+        <v>0.3</v>
+      </c>
+      <c r="W51">
+        <v>0.0336</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>7.965036664016255</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.113099709298835</v>
+      </c>
+      <c r="C52">
+        <v>2.210329052833234</v>
+      </c>
+      <c r="D52">
+        <v>3.750329052833234</v>
+      </c>
+      <c r="E52">
+        <v>1.54</v>
+      </c>
+      <c r="F52">
+        <v>1.54</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>3.08</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.68</v>
+      </c>
+      <c r="K52">
+        <v>1.103</v>
+      </c>
+      <c r="L52">
+        <v>0.577</v>
+      </c>
+      <c r="M52">
+        <v>0.07392</v>
+      </c>
+      <c r="N52">
+        <v>0.50308</v>
+      </c>
+      <c r="O52">
+        <v>0.150924</v>
+      </c>
+      <c r="P52">
+        <v>0.352156</v>
+      </c>
+      <c r="Q52">
+        <v>1.455156</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.19259941859767</v>
+      </c>
+      <c r="T52">
+        <v>1.21632906344099</v>
+      </c>
+      <c r="U52">
+        <v>0.048</v>
+      </c>
+      <c r="V52">
+        <v>0.3</v>
+      </c>
+      <c r="W52">
+        <v>0.0336</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>7.80573593073593</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1133117985601332</v>
+      </c>
+      <c r="C53">
+        <v>2.168854172695978</v>
+      </c>
+      <c r="D53">
+        <v>3.739654172695978</v>
+      </c>
+      <c r="E53">
+        <v>1.5708</v>
+      </c>
+      <c r="F53">
+        <v>1.5708</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>3.08</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.68</v>
+      </c>
+      <c r="K53">
+        <v>1.103</v>
+      </c>
+      <c r="L53">
+        <v>0.577</v>
+      </c>
+      <c r="M53">
+        <v>0.07775460000000001</v>
+      </c>
+      <c r="N53">
+        <v>0.4992454</v>
+      </c>
+      <c r="O53">
+        <v>0.14977362</v>
+      </c>
+      <c r="P53">
+        <v>0.34947178</v>
+      </c>
+      <c r="Q53">
+        <v>1.45247178</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1951842827757821</v>
+      </c>
+      <c r="T53">
+        <v>1.236771568708906</v>
+      </c>
+      <c r="U53">
+        <v>0.0495</v>
+      </c>
+      <c r="V53">
+        <v>0.3</v>
+      </c>
+      <c r="W53">
+        <v>0.03465</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>7.420782821852339</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1129988878214314</v>
+      </c>
+      <c r="C54">
+        <v>2.153825001397397</v>
+      </c>
+      <c r="D54">
+        <v>3.755425001397397</v>
+      </c>
+      <c r="E54">
+        <v>1.6016</v>
+      </c>
+      <c r="F54">
+        <v>1.6016</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>3.08</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.68</v>
+      </c>
+      <c r="K54">
+        <v>1.103</v>
+      </c>
+      <c r="L54">
+        <v>0.577</v>
+      </c>
+      <c r="M54">
+        <v>0.07927920000000001</v>
+      </c>
+      <c r="N54">
+        <v>0.4977208</v>
+      </c>
+      <c r="O54">
+        <v>0.14931624</v>
+      </c>
+      <c r="P54">
+        <v>0.34840456</v>
+      </c>
+      <c r="Q54">
+        <v>1.45140456</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1978768496279822</v>
+      </c>
+      <c r="T54">
+        <v>1.258065845029651</v>
+      </c>
+      <c r="U54">
+        <v>0.0495</v>
+      </c>
+      <c r="V54">
+        <v>0.3</v>
+      </c>
+      <c r="W54">
+        <v>0.03465</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>7.278075459893641</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1126859770827297</v>
+      </c>
+      <c r="C55">
+        <v>2.138929410565736</v>
+      </c>
+      <c r="D55">
+        <v>3.771329410565736</v>
+      </c>
+      <c r="E55">
+        <v>1.6324</v>
+      </c>
+      <c r="F55">
+        <v>1.6324</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>3.08</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.68</v>
+      </c>
+      <c r="K55">
+        <v>1.103</v>
+      </c>
+      <c r="L55">
+        <v>0.577</v>
+      </c>
+      <c r="M55">
+        <v>0.08080380000000001</v>
+      </c>
+      <c r="N55">
+        <v>0.4961962</v>
+      </c>
+      <c r="O55">
+        <v>0.14885886</v>
+      </c>
+      <c r="P55">
+        <v>0.34733734</v>
+      </c>
+      <c r="Q55">
+        <v>1.45033734</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2006839937930419</v>
+      </c>
+      <c r="T55">
+        <v>1.280266260768301</v>
+      </c>
+      <c r="U55">
+        <v>0.0495</v>
+      </c>
+      <c r="V55">
+        <v>0.3</v>
+      </c>
+      <c r="W55">
+        <v>0.03465</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>7.140753281405082</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1123730663440279</v>
+      </c>
+      <c r="C56">
+        <v>2.124169104578621</v>
+      </c>
+      <c r="D56">
+        <v>3.787369104578621</v>
+      </c>
+      <c r="E56">
+        <v>1.6632</v>
+      </c>
+      <c r="F56">
+        <v>1.6632</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>3.08</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.68</v>
+      </c>
+      <c r="K56">
+        <v>1.103</v>
+      </c>
+      <c r="L56">
+        <v>0.577</v>
+      </c>
+      <c r="M56">
+        <v>0.08232840000000001</v>
+      </c>
+      <c r="N56">
+        <v>0.4946715999999999</v>
+      </c>
+      <c r="O56">
+        <v>0.14840148</v>
+      </c>
+      <c r="P56">
+        <v>0.34627012</v>
+      </c>
+      <c r="Q56">
+        <v>1.44927012</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2036131877044085</v>
+      </c>
+      <c r="T56">
+        <v>1.303431911973848</v>
+      </c>
+      <c r="U56">
+        <v>0.0495</v>
+      </c>
+      <c r="V56">
+        <v>0.3</v>
+      </c>
+      <c r="W56">
+        <v>0.03465</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>7.008517109527209</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1120601556053261</v>
+      </c>
+      <c r="C57">
+        <v>2.109545816932803</v>
+      </c>
+      <c r="D57">
+        <v>3.803545816932803</v>
+      </c>
+      <c r="E57">
+        <v>1.694</v>
+      </c>
+      <c r="F57">
+        <v>1.694</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>3.08</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.68</v>
+      </c>
+      <c r="K57">
+        <v>1.103</v>
+      </c>
+      <c r="L57">
+        <v>0.577</v>
+      </c>
+      <c r="M57">
+        <v>0.08385300000000001</v>
+      </c>
+      <c r="N57">
+        <v>0.4931469999999999</v>
+      </c>
+      <c r="O57">
+        <v>0.1479441</v>
+      </c>
+      <c r="P57">
+        <v>0.3452029</v>
+      </c>
+      <c r="Q57">
+        <v>1.4482029</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2066725680118359</v>
+      </c>
+      <c r="T57">
+        <v>1.32762714767742</v>
+      </c>
+      <c r="U57">
+        <v>0.0495</v>
+      </c>
+      <c r="V57">
+        <v>0.3</v>
+      </c>
+      <c r="W57">
+        <v>0.03465</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>6.881089525717623</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1117472448666244</v>
+      </c>
+      <c r="C58">
+        <v>2.095061310868708</v>
+      </c>
+      <c r="D58">
+        <v>3.819861310868708</v>
+      </c>
+      <c r="E58">
+        <v>1.7248</v>
+      </c>
+      <c r="F58">
+        <v>1.7248</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>3.08</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.68</v>
+      </c>
+      <c r="K58">
+        <v>1.103</v>
+      </c>
+      <c r="L58">
+        <v>0.577</v>
+      </c>
+      <c r="M58">
+        <v>0.08537760000000001</v>
+      </c>
+      <c r="N58">
+        <v>0.4916224</v>
+      </c>
+      <c r="O58">
+        <v>0.14748672</v>
+      </c>
+      <c r="P58">
+        <v>0.3441356799999999</v>
+      </c>
+      <c r="Q58">
+        <v>1.44713568</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.20987101106051</v>
+      </c>
+      <c r="T58">
+        <v>1.352922166822064</v>
+      </c>
+      <c r="U58">
+        <v>0.0495</v>
+      </c>
+      <c r="V58">
+        <v>0.3</v>
+      </c>
+      <c r="W58">
+        <v>0.03465</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>6.758212927044094</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1114343341279226</v>
+      </c>
+      <c r="C59">
+        <v>2.080717380011122</v>
+      </c>
+      <c r="D59">
+        <v>3.836317380011122</v>
+      </c>
+      <c r="E59">
+        <v>1.7556</v>
+      </c>
+      <c r="F59">
+        <v>1.7556</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>3.08</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.68</v>
+      </c>
+      <c r="K59">
+        <v>1.103</v>
+      </c>
+      <c r="L59">
+        <v>0.577</v>
+      </c>
+      <c r="M59">
+        <v>0.08690220000000001</v>
+      </c>
+      <c r="N59">
+        <v>0.4900977999999999</v>
+      </c>
+      <c r="O59">
+        <v>0.14702934</v>
+      </c>
+      <c r="P59">
+        <v>0.3430684599999999</v>
+      </c>
+      <c r="Q59">
+        <v>1.44606846</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2132182189021456</v>
+      </c>
+      <c r="T59">
+        <v>1.379393698485063</v>
+      </c>
+      <c r="U59">
+        <v>0.0495</v>
+      </c>
+      <c r="V59">
+        <v>0.3</v>
+      </c>
+      <c r="W59">
+        <v>0.03465</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>6.639647787973145</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1111214233892208</v>
+      </c>
+      <c r="C60">
+        <v>2.066515849026497</v>
+      </c>
+      <c r="D60">
+        <v>3.852915849026497</v>
+      </c>
+      <c r="E60">
+        <v>1.7864</v>
+      </c>
+      <c r="F60">
+        <v>1.7864</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>3.08</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.68</v>
+      </c>
+      <c r="K60">
+        <v>1.103</v>
+      </c>
+      <c r="L60">
+        <v>0.577</v>
+      </c>
+      <c r="M60">
+        <v>0.0884268</v>
+      </c>
+      <c r="N60">
+        <v>0.4885731999999999</v>
+      </c>
+      <c r="O60">
+        <v>0.14657196</v>
+      </c>
+      <c r="P60">
+        <v>0.34200124</v>
+      </c>
+      <c r="Q60">
+        <v>1.44500124</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2167248175933829</v>
+      </c>
+      <c r="T60">
+        <v>1.40712577927487</v>
+      </c>
+      <c r="U60">
+        <v>0.0495</v>
+      </c>
+      <c r="V60">
+        <v>0.3</v>
+      </c>
+      <c r="W60">
+        <v>0.03465</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>6.525171101973609</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.110808512650519</v>
+      </c>
+      <c r="C61">
+        <v>2.052458574297409</v>
+      </c>
+      <c r="D61">
+        <v>3.869658574297409</v>
+      </c>
+      <c r="E61">
+        <v>1.8172</v>
+      </c>
+      <c r="F61">
+        <v>1.8172</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>3.08</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.68</v>
+      </c>
+      <c r="K61">
+        <v>1.103</v>
+      </c>
+      <c r="L61">
+        <v>0.577</v>
+      </c>
+      <c r="M61">
+        <v>0.0899514</v>
+      </c>
+      <c r="N61">
+        <v>0.4870485999999999</v>
+      </c>
+      <c r="O61">
+        <v>0.14611458</v>
+      </c>
+      <c r="P61">
+        <v>0.3409340199999999</v>
+      </c>
+      <c r="Q61">
+        <v>1.44393402</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2204024698793147</v>
+      </c>
+      <c r="T61">
+        <v>1.43621064449345</v>
+      </c>
+      <c r="U61">
+        <v>0.0495</v>
+      </c>
+      <c r="V61">
+        <v>0.3</v>
+      </c>
+      <c r="W61">
+        <v>0.03465</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>6.414574981601175</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1104956019118173</v>
+      </c>
+      <c r="C62">
+        <v>2.038547444614675</v>
+      </c>
+      <c r="D62">
+        <v>3.886547444614675</v>
+      </c>
+      <c r="E62">
+        <v>1.848</v>
+      </c>
+      <c r="F62">
+        <v>1.848</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>3.08</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.68</v>
+      </c>
+      <c r="K62">
+        <v>1.103</v>
+      </c>
+      <c r="L62">
+        <v>0.577</v>
+      </c>
+      <c r="M62">
+        <v>0.091476</v>
+      </c>
+      <c r="N62">
+        <v>0.485524</v>
+      </c>
+      <c r="O62">
+        <v>0.1456572</v>
+      </c>
+      <c r="P62">
+        <v>0.3398668</v>
+      </c>
+      <c r="Q62">
+        <v>1.4428668</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2242640047795432</v>
+      </c>
+      <c r="T62">
+        <v>1.466749752972958</v>
+      </c>
+      <c r="U62">
+        <v>0.0495</v>
+      </c>
+      <c r="V62">
+        <v>0.3</v>
+      </c>
+      <c r="W62">
+        <v>0.03465</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>6.307665398574489</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1101826911731155</v>
+      </c>
+      <c r="C63">
+        <v>2.024784381887669</v>
+      </c>
+      <c r="D63">
+        <v>3.903584381887669</v>
+      </c>
+      <c r="E63">
+        <v>1.8788</v>
+      </c>
+      <c r="F63">
+        <v>1.8788</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>3.08</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.68</v>
+      </c>
+      <c r="K63">
+        <v>1.103</v>
+      </c>
+      <c r="L63">
+        <v>0.577</v>
+      </c>
+      <c r="M63">
+        <v>0.0930006</v>
+      </c>
+      <c r="N63">
+        <v>0.4839994</v>
+      </c>
+      <c r="O63">
+        <v>0.14519982</v>
+      </c>
+      <c r="P63">
+        <v>0.33879958</v>
+      </c>
+      <c r="Q63">
+        <v>1.44179958</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2283235671105526</v>
+      </c>
+      <c r="T63">
+        <v>1.498854969579621</v>
+      </c>
+      <c r="U63">
+        <v>0.0495</v>
+      </c>
+      <c r="V63">
+        <v>0.3</v>
+      </c>
+      <c r="W63">
+        <v>0.03465</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>6.204261047778186</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1104773804344137</v>
+      </c>
+      <c r="C64">
+        <v>1.977935463931378</v>
+      </c>
+      <c r="D64">
+        <v>3.887535463931377</v>
+      </c>
+      <c r="E64">
+        <v>1.9096</v>
+      </c>
+      <c r="F64">
+        <v>1.9096</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>3.08</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.68</v>
+      </c>
+      <c r="K64">
+        <v>1.103</v>
+      </c>
+      <c r="L64">
+        <v>0.577</v>
+      </c>
+      <c r="M64">
+        <v>0.09719864</v>
+      </c>
+      <c r="N64">
+        <v>0.47980136</v>
+      </c>
+      <c r="O64">
+        <v>0.143940408</v>
+      </c>
+      <c r="P64">
+        <v>0.335860952</v>
+      </c>
+      <c r="Q64">
+        <v>1.438860952</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2325967906168783</v>
+      </c>
+      <c r="T64">
+        <v>1.532649934428739</v>
+      </c>
+      <c r="U64">
+        <v>0.0509</v>
+      </c>
+      <c r="V64">
+        <v>0.3</v>
+      </c>
+      <c r="W64">
+        <v>0.03563</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.936297051069849</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.110174269695712</v>
+      </c>
+      <c r="C65">
+        <v>1.963644967303184</v>
+      </c>
+      <c r="D65">
+        <v>3.904044967303184</v>
+      </c>
+      <c r="E65">
+        <v>1.9404</v>
+      </c>
+      <c r="F65">
+        <v>1.9404</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>3.08</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.68</v>
+      </c>
+      <c r="K65">
+        <v>1.103</v>
+      </c>
+      <c r="L65">
+        <v>0.577</v>
+      </c>
+      <c r="M65">
+        <v>0.09876636000000001</v>
+      </c>
+      <c r="N65">
+        <v>0.47823364</v>
+      </c>
+      <c r="O65">
+        <v>0.143470092</v>
+      </c>
+      <c r="P65">
+        <v>0.334763548</v>
+      </c>
+      <c r="Q65">
+        <v>1.437763548</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2371009991775999</v>
+      </c>
+      <c r="T65">
+        <v>1.568271654134567</v>
+      </c>
+      <c r="U65">
+        <v>0.0509</v>
+      </c>
+      <c r="V65">
+        <v>0.3</v>
+      </c>
+      <c r="W65">
+        <v>0.03563</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.84207011375128</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1098711589570102</v>
+      </c>
+      <c r="C66">
+        <v>1.949495293136199</v>
+      </c>
+      <c r="D66">
+        <v>3.920695293136199</v>
+      </c>
+      <c r="E66">
+        <v>1.9712</v>
+      </c>
+      <c r="F66">
+        <v>1.9712</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>3.08</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.68</v>
+      </c>
+      <c r="K66">
+        <v>1.103</v>
+      </c>
+      <c r="L66">
+        <v>0.577</v>
+      </c>
+      <c r="M66">
+        <v>0.10033408</v>
+      </c>
+      <c r="N66">
+        <v>0.47666592</v>
+      </c>
+      <c r="O66">
+        <v>0.142999776</v>
+      </c>
+      <c r="P66">
+        <v>0.3336661439999999</v>
+      </c>
+      <c r="Q66">
+        <v>1.436666144</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2418554415472506</v>
+      </c>
+      <c r="T66">
+        <v>1.605872358268497</v>
+      </c>
+      <c r="U66">
+        <v>0.0509</v>
+      </c>
+      <c r="V66">
+        <v>0.3</v>
+      </c>
+      <c r="W66">
+        <v>0.03563</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.750787768223917</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1095680482183084</v>
+      </c>
+      <c r="C67">
+        <v>1.935488250925016</v>
+      </c>
+      <c r="D67">
+        <v>3.937488250925016</v>
+      </c>
+      <c r="E67">
+        <v>2.002</v>
+      </c>
+      <c r="F67">
+        <v>2.002</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>3.08</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.68</v>
+      </c>
+      <c r="K67">
+        <v>1.103</v>
+      </c>
+      <c r="L67">
+        <v>0.577</v>
+      </c>
+      <c r="M67">
+        <v>0.1019018</v>
+      </c>
+      <c r="N67">
+        <v>0.4750981999999999</v>
+      </c>
+      <c r="O67">
+        <v>0.14252946</v>
+      </c>
+      <c r="P67">
+        <v>0.3325687399999999</v>
+      </c>
+      <c r="Q67">
+        <v>1.43556874</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2468815663380241</v>
+      </c>
+      <c r="T67">
+        <v>1.645621674067222</v>
+      </c>
+      <c r="U67">
+        <v>0.0509</v>
+      </c>
+      <c r="V67">
+        <v>0.3</v>
+      </c>
+      <c r="W67">
+        <v>0.03563</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.66231411025124</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1092649374796067</v>
+      </c>
+      <c r="C68">
+        <v>1.921625681298992</v>
+      </c>
+      <c r="D68">
+        <v>3.954425681298992</v>
+      </c>
+      <c r="E68">
+        <v>2.0328</v>
+      </c>
+      <c r="F68">
+        <v>2.0328</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>3.08</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.68</v>
+      </c>
+      <c r="K68">
+        <v>1.103</v>
+      </c>
+      <c r="L68">
+        <v>0.577</v>
+      </c>
+      <c r="M68">
+        <v>0.10346952</v>
+      </c>
+      <c r="N68">
+        <v>0.47353048</v>
+      </c>
+      <c r="O68">
+        <v>0.142059144</v>
+      </c>
+      <c r="P68">
+        <v>0.331471336</v>
+      </c>
+      <c r="Q68">
+        <v>1.434471336</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2522033455282549</v>
+      </c>
+      <c r="T68">
+        <v>1.687709184912931</v>
+      </c>
+      <c r="U68">
+        <v>0.0509</v>
+      </c>
+      <c r="V68">
+        <v>0.3</v>
+      </c>
+      <c r="W68">
+        <v>0.03563</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>5.576521472217133</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1089618267409049</v>
+      </c>
+      <c r="C69">
+        <v>1.90790945669478</v>
+      </c>
+      <c r="D69">
+        <v>3.97150945669478</v>
+      </c>
+      <c r="E69">
+        <v>2.0636</v>
+      </c>
+      <c r="F69">
+        <v>2.0636</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>3.08</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.68</v>
+      </c>
+      <c r="K69">
+        <v>1.103</v>
+      </c>
+      <c r="L69">
+        <v>0.577</v>
+      </c>
+      <c r="M69">
+        <v>0.10503724</v>
+      </c>
+      <c r="N69">
+        <v>0.4719627599999999</v>
+      </c>
+      <c r="O69">
+        <v>0.141588828</v>
+      </c>
+      <c r="P69">
+        <v>0.330373932</v>
+      </c>
+      <c r="Q69">
+        <v>1.433373932</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2578476567906209</v>
+      </c>
+      <c r="T69">
+        <v>1.732347453991713</v>
+      </c>
+      <c r="U69">
+        <v>0.0509</v>
+      </c>
+      <c r="V69">
+        <v>0.3</v>
+      </c>
+      <c r="W69">
+        <v>0.03563</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.493289808452697</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1086587160022031</v>
+      </c>
+      <c r="C70">
+        <v>1.894341482046374</v>
+      </c>
+      <c r="D70">
+        <v>3.988741482046374</v>
+      </c>
+      <c r="E70">
+        <v>2.0944</v>
+      </c>
+      <c r="F70">
+        <v>2.0944</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>3.08</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.68</v>
+      </c>
+      <c r="K70">
+        <v>1.103</v>
+      </c>
+      <c r="L70">
+        <v>0.577</v>
+      </c>
+      <c r="M70">
+        <v>0.10660496</v>
+      </c>
+      <c r="N70">
+        <v>0.4703950399999999</v>
+      </c>
+      <c r="O70">
+        <v>0.141118512</v>
+      </c>
+      <c r="P70">
+        <v>0.329276528</v>
+      </c>
+      <c r="Q70">
+        <v>1.432276528</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2638447375068848</v>
+      </c>
+      <c r="T70">
+        <v>1.779775614887919</v>
+      </c>
+      <c r="U70">
+        <v>0.0509</v>
+      </c>
+      <c r="V70">
+        <v>0.3</v>
+      </c>
+      <c r="W70">
+        <v>0.03563</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.41250613479898</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1083556052635014</v>
+      </c>
+      <c r="C71">
+        <v>1.880923695493202</v>
+      </c>
+      <c r="D71">
+        <v>4.006123695493202</v>
+      </c>
+      <c r="E71">
+        <v>2.1252</v>
+      </c>
+      <c r="F71">
+        <v>2.1252</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>3.08</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.68</v>
+      </c>
+      <c r="K71">
+        <v>1.103</v>
+      </c>
+      <c r="L71">
+        <v>0.577</v>
+      </c>
+      <c r="M71">
+        <v>0.10817268</v>
+      </c>
+      <c r="N71">
+        <v>0.4688273199999999</v>
+      </c>
+      <c r="O71">
+        <v>0.140648196</v>
+      </c>
+      <c r="P71">
+        <v>0.3281791239999999</v>
+      </c>
+      <c r="Q71">
+        <v>1.431179124</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.270228726656456</v>
+      </c>
+      <c r="T71">
+        <v>1.830263657132268</v>
+      </c>
+      <c r="U71">
+        <v>0.0509</v>
+      </c>
+      <c r="V71">
+        <v>0.3</v>
+      </c>
+      <c r="W71">
+        <v>0.03563</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>5.334064016903342</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1080524945247996</v>
+      </c>
+      <c r="C72">
+        <v>1.867658069106803</v>
+      </c>
+      <c r="D72">
+        <v>4.023658069106803</v>
+      </c>
+      <c r="E72">
+        <v>2.156</v>
+      </c>
+      <c r="F72">
+        <v>2.156</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>3.08</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.68</v>
+      </c>
+      <c r="K72">
+        <v>1.103</v>
+      </c>
+      <c r="L72">
+        <v>0.577</v>
+      </c>
+      <c r="M72">
+        <v>0.1097404</v>
+      </c>
+      <c r="N72">
+        <v>0.4672595999999999</v>
+      </c>
+      <c r="O72">
+        <v>0.14017788</v>
+      </c>
+      <c r="P72">
+        <v>0.32708172</v>
+      </c>
+      <c r="Q72">
+        <v>1.43008172</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2770383150826653</v>
+      </c>
+      <c r="T72">
+        <v>1.884117568859573</v>
+      </c>
+      <c r="U72">
+        <v>0.0509</v>
+      </c>
+      <c r="V72">
+        <v>0.3</v>
+      </c>
+      <c r="W72">
+        <v>0.03563</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.257863102376152</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1077493837860978</v>
+      </c>
+      <c r="C73">
+        <v>1.854546609636677</v>
+      </c>
+      <c r="D73">
+        <v>4.041346609636677</v>
+      </c>
+      <c r="E73">
+        <v>2.1868</v>
+      </c>
+      <c r="F73">
+        <v>2.1868</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>3.08</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.68</v>
+      </c>
+      <c r="K73">
+        <v>1.103</v>
+      </c>
+      <c r="L73">
+        <v>0.577</v>
+      </c>
+      <c r="M73">
+        <v>0.11130812</v>
+      </c>
+      <c r="N73">
+        <v>0.4656918799999999</v>
+      </c>
+      <c r="O73">
+        <v>0.139707564</v>
+      </c>
+      <c r="P73">
+        <v>0.325984316</v>
+      </c>
+      <c r="Q73">
+        <v>1.428984316</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.284317530296889</v>
+      </c>
+      <c r="T73">
+        <v>1.941685543464623</v>
+      </c>
+      <c r="U73">
+        <v>0.0509</v>
+      </c>
+      <c r="V73">
+        <v>0.3</v>
+      </c>
+      <c r="W73">
+        <v>0.03563</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.183808692483531</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1074462730473961</v>
+      </c>
+      <c r="C74">
+        <v>1.841591359275904</v>
+      </c>
+      <c r="D74">
+        <v>4.059191359275904</v>
+      </c>
+      <c r="E74">
+        <v>2.2176</v>
+      </c>
+      <c r="F74">
+        <v>2.2176</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>3.08</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.68</v>
+      </c>
+      <c r="K74">
+        <v>1.103</v>
+      </c>
+      <c r="L74">
+        <v>0.577</v>
+      </c>
+      <c r="M74">
+        <v>0.11287584</v>
+      </c>
+      <c r="N74">
+        <v>0.46412416</v>
+      </c>
+      <c r="O74">
+        <v>0.139237248</v>
+      </c>
+      <c r="P74">
+        <v>0.324886912</v>
+      </c>
+      <c r="Q74">
+        <v>1.427886912</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2921166894549859</v>
+      </c>
+      <c r="T74">
+        <v>2.003365516255748</v>
+      </c>
+      <c r="U74">
+        <v>0.0509</v>
+      </c>
+      <c r="V74">
+        <v>0.3</v>
+      </c>
+      <c r="W74">
+        <v>0.03563</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>5.11181134953237</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1071431623086943</v>
+      </c>
+      <c r="C75">
+        <v>1.828794396447122</v>
+      </c>
+      <c r="D75">
+        <v>4.077194396447122</v>
+      </c>
+      <c r="E75">
+        <v>2.2484</v>
+      </c>
+      <c r="F75">
+        <v>2.2484</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>3.08</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.68</v>
+      </c>
+      <c r="K75">
+        <v>1.103</v>
+      </c>
+      <c r="L75">
+        <v>0.577</v>
+      </c>
+      <c r="M75">
+        <v>0.11444356</v>
+      </c>
+      <c r="N75">
+        <v>0.46255644</v>
+      </c>
+      <c r="O75">
+        <v>0.138766932</v>
+      </c>
+      <c r="P75">
+        <v>0.3237895079999999</v>
+      </c>
+      <c r="Q75">
+        <v>1.426789508</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3004935641062751</v>
+      </c>
+      <c r="T75">
+        <v>2.06961437592029</v>
+      </c>
+      <c r="U75">
+        <v>0.0509</v>
+      </c>
+      <c r="V75">
+        <v>0.3</v>
+      </c>
+      <c r="W75">
+        <v>0.03563</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>5.041786536525078</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1068400515699925</v>
+      </c>
+      <c r="C76">
+        <v>1.816157836609519</v>
+      </c>
+      <c r="D76">
+        <v>4.095357836609518</v>
+      </c>
+      <c r="E76">
+        <v>2.2792</v>
+      </c>
+      <c r="F76">
+        <v>2.2792</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>3.08</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.68</v>
+      </c>
+      <c r="K76">
+        <v>1.103</v>
+      </c>
+      <c r="L76">
+        <v>0.577</v>
+      </c>
+      <c r="M76">
+        <v>0.11601128</v>
+      </c>
+      <c r="N76">
+        <v>0.46098872</v>
+      </c>
+      <c r="O76">
+        <v>0.138296616</v>
+      </c>
+      <c r="P76">
+        <v>0.322692104</v>
+      </c>
+      <c r="Q76">
+        <v>1.425692104</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3095148137307404</v>
+      </c>
+      <c r="T76">
+        <v>2.140959301712873</v>
+      </c>
+      <c r="U76">
+        <v>0.0509</v>
+      </c>
+      <c r="V76">
+        <v>0.3</v>
+      </c>
+      <c r="W76">
+        <v>0.03563</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.973654286031496</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1065369408312907</v>
+      </c>
+      <c r="C77">
+        <v>1.803683833087489</v>
+      </c>
+      <c r="D77">
+        <v>4.113683833087489</v>
+      </c>
+      <c r="E77">
+        <v>2.31</v>
+      </c>
+      <c r="F77">
+        <v>2.31</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>3.08</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.68</v>
+      </c>
+      <c r="K77">
+        <v>1.103</v>
+      </c>
+      <c r="L77">
+        <v>0.577</v>
+      </c>
+      <c r="M77">
+        <v>0.117579</v>
+      </c>
+      <c r="N77">
+        <v>0.459421</v>
+      </c>
+      <c r="O77">
+        <v>0.1378263</v>
+      </c>
+      <c r="P77">
+        <v>0.3215947</v>
+      </c>
+      <c r="Q77">
+        <v>1.4245947</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3192577633251629</v>
+      </c>
+      <c r="T77">
+        <v>2.218011821568864</v>
+      </c>
+      <c r="U77">
+        <v>0.0509</v>
+      </c>
+      <c r="V77">
+        <v>0.3</v>
+      </c>
+      <c r="W77">
+        <v>0.03563</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.907338895551076</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.106233830092589</v>
+      </c>
+      <c r="C78">
+        <v>1.791374577921655</v>
+      </c>
+      <c r="D78">
+        <v>4.132174577921655</v>
+      </c>
+      <c r="E78">
+        <v>2.3408</v>
+      </c>
+      <c r="F78">
+        <v>2.3408</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>3.08</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.68</v>
+      </c>
+      <c r="K78">
+        <v>1.103</v>
+      </c>
+      <c r="L78">
+        <v>0.577</v>
+      </c>
+      <c r="M78">
+        <v>0.11914672</v>
+      </c>
+      <c r="N78">
+        <v>0.4578532799999999</v>
+      </c>
+      <c r="O78">
+        <v>0.137355984</v>
+      </c>
+      <c r="P78">
+        <v>0.320497296</v>
+      </c>
+      <c r="Q78">
+        <v>1.423497296</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3298126253857874</v>
+      </c>
+      <c r="T78">
+        <v>2.301485384746187</v>
+      </c>
+      <c r="U78">
+        <v>0.0509</v>
+      </c>
+      <c r="V78">
+        <v>0.3</v>
+      </c>
+      <c r="W78">
+        <v>0.03563</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.842768646925403</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1059307193538872</v>
+      </c>
+      <c r="C79">
+        <v>1.779232302742924</v>
+      </c>
+      <c r="D79">
+        <v>4.150832302742923</v>
+      </c>
+      <c r="E79">
+        <v>2.3716</v>
+      </c>
+      <c r="F79">
+        <v>2.3716</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>3.08</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.68</v>
+      </c>
+      <c r="K79">
+        <v>1.103</v>
+      </c>
+      <c r="L79">
+        <v>0.577</v>
+      </c>
+      <c r="M79">
+        <v>0.12071444</v>
+      </c>
+      <c r="N79">
+        <v>0.45628556</v>
+      </c>
+      <c r="O79">
+        <v>0.136885668</v>
+      </c>
+      <c r="P79">
+        <v>0.319399892</v>
+      </c>
+      <c r="Q79">
+        <v>1.422399892</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.34128530153864</v>
+      </c>
+      <c r="T79">
+        <v>2.392217518634581</v>
+      </c>
+      <c r="U79">
+        <v>0.0509</v>
+      </c>
+      <c r="V79">
+        <v>0.3</v>
+      </c>
+      <c r="W79">
+        <v>0.03563</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.779875547614685</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1056276086151854</v>
+      </c>
+      <c r="C80">
+        <v>1.767259279670325</v>
+      </c>
+      <c r="D80">
+        <v>4.169659279670325</v>
+      </c>
+      <c r="E80">
+        <v>2.4024</v>
+      </c>
+      <c r="F80">
+        <v>2.4024</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>3.08</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.68</v>
+      </c>
+      <c r="K80">
+        <v>1.103</v>
+      </c>
+      <c r="L80">
+        <v>0.577</v>
+      </c>
+      <c r="M80">
+        <v>0.12228216</v>
+      </c>
+      <c r="N80">
+        <v>0.4547178399999999</v>
+      </c>
+      <c r="O80">
+        <v>0.136415352</v>
+      </c>
+      <c r="P80">
+        <v>0.3183024879999999</v>
+      </c>
+      <c r="Q80">
+        <v>1.421302488</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3538009482508429</v>
+      </c>
+      <c r="T80">
+        <v>2.491198028331012</v>
+      </c>
+      <c r="U80">
+        <v>0.0509</v>
+      </c>
+      <c r="V80">
+        <v>0.3</v>
+      </c>
+      <c r="W80">
+        <v>0.03563</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>4.718595091876034</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1053244978764836</v>
+      </c>
+      <c r="C81">
+        <v>1.755457822233431</v>
+      </c>
+      <c r="D81">
+        <v>4.188657822233432</v>
+      </c>
+      <c r="E81">
+        <v>2.4332</v>
+      </c>
+      <c r="F81">
+        <v>2.4332</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>3.08</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.68</v>
+      </c>
+      <c r="K81">
+        <v>1.103</v>
+      </c>
+      <c r="L81">
+        <v>0.577</v>
+      </c>
+      <c r="M81">
+        <v>0.12384988</v>
+      </c>
+      <c r="N81">
+        <v>0.4531501199999999</v>
+      </c>
+      <c r="O81">
+        <v>0.135945036</v>
+      </c>
+      <c r="P81">
+        <v>0.317205084</v>
+      </c>
+      <c r="Q81">
+        <v>1.420205084</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3675085613165888</v>
+      </c>
+      <c r="T81">
+        <v>2.599605253236626</v>
+      </c>
+      <c r="U81">
+        <v>0.0509</v>
+      </c>
+      <c r="V81">
+        <v>0.3</v>
+      </c>
+      <c r="W81">
+        <v>0.03563</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>4.658866040080134</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1050213871377819</v>
+      </c>
+      <c r="C82">
+        <v>1.743830286320064</v>
+      </c>
+      <c r="D82">
+        <v>4.207830286320064</v>
+      </c>
+      <c r="E82">
+        <v>2.464</v>
+      </c>
+      <c r="F82">
+        <v>2.464</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>3.08</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.68</v>
+      </c>
+      <c r="K82">
+        <v>1.103</v>
+      </c>
+      <c r="L82">
+        <v>0.577</v>
+      </c>
+      <c r="M82">
+        <v>0.1254176</v>
+      </c>
+      <c r="N82">
+        <v>0.4515823999999999</v>
+      </c>
+      <c r="O82">
+        <v>0.13547472</v>
+      </c>
+      <c r="P82">
+        <v>0.31610768</v>
+      </c>
+      <c r="Q82">
+        <v>1.41910768</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3825869356889094</v>
+      </c>
+      <c r="T82">
+        <v>2.718853200632801</v>
+      </c>
+      <c r="U82">
+        <v>0.0509</v>
+      </c>
+      <c r="V82">
+        <v>0.3</v>
+      </c>
+      <c r="W82">
+        <v>0.03563</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>4.600630214579133</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1047182763990801</v>
+      </c>
+      <c r="C83">
+        <v>1.732379071150183</v>
+      </c>
+      <c r="D83">
+        <v>4.227179071150183</v>
+      </c>
+      <c r="E83">
+        <v>2.4948</v>
+      </c>
+      <c r="F83">
+        <v>2.4948</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>3.08</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.68</v>
+      </c>
+      <c r="K83">
+        <v>1.103</v>
+      </c>
+      <c r="L83">
+        <v>0.577</v>
+      </c>
+      <c r="M83">
+        <v>0.12698532</v>
+      </c>
+      <c r="N83">
+        <v>0.4500146799999999</v>
+      </c>
+      <c r="O83">
+        <v>0.135004404</v>
+      </c>
+      <c r="P83">
+        <v>0.315010276</v>
+      </c>
+      <c r="Q83">
+        <v>1.418010276</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3992525073635796</v>
+      </c>
+      <c r="T83">
+        <v>2.850653563544364</v>
+      </c>
+      <c r="U83">
+        <v>0.0509</v>
+      </c>
+      <c r="V83">
+        <v>0.3</v>
+      </c>
+      <c r="W83">
+        <v>0.03563</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>4.54383231069544</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1059075656603783</v>
+      </c>
+      <c r="C84">
+        <v>1.626664437823352</v>
+      </c>
+      <c r="D84">
+        <v>4.152264437823352</v>
+      </c>
+      <c r="E84">
+        <v>2.5256</v>
+      </c>
+      <c r="F84">
+        <v>2.5256</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>3.08</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.68</v>
+      </c>
+      <c r="K84">
+        <v>1.103</v>
+      </c>
+      <c r="L84">
+        <v>0.577</v>
+      </c>
+      <c r="M84">
+        <v>0.1351196</v>
+      </c>
+      <c r="N84">
+        <v>0.4418804</v>
+      </c>
+      <c r="O84">
+        <v>0.13256412</v>
+      </c>
+      <c r="P84">
+        <v>0.30931628</v>
+      </c>
+      <c r="Q84">
+        <v>1.41231628</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4177698092243242</v>
+      </c>
+      <c r="T84">
+        <v>2.997098411223878</v>
+      </c>
+      <c r="U84">
+        <v>0.0535</v>
+      </c>
+      <c r="V84">
+        <v>0.3</v>
+      </c>
+      <c r="W84">
+        <v>0.03745</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>4.270290912643317</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1056226549216766</v>
+      </c>
+      <c r="C85">
+        <v>1.613568384630792</v>
+      </c>
+      <c r="D85">
+        <v>4.169968384630793</v>
+      </c>
+      <c r="E85">
+        <v>2.5564</v>
+      </c>
+      <c r="F85">
+        <v>2.5564</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>3.08</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.68</v>
+      </c>
+      <c r="K85">
+        <v>1.103</v>
+      </c>
+      <c r="L85">
+        <v>0.577</v>
+      </c>
+      <c r="M85">
+        <v>0.1367674</v>
+      </c>
+      <c r="N85">
+        <v>0.4402326</v>
+      </c>
+      <c r="O85">
+        <v>0.13206978</v>
+      </c>
+      <c r="P85">
+        <v>0.3081628199999999</v>
+      </c>
+      <c r="Q85">
+        <v>1.41116282</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4384656171863329</v>
+      </c>
+      <c r="T85">
+        <v>3.160772064512746</v>
+      </c>
+      <c r="U85">
+        <v>0.0535</v>
+      </c>
+      <c r="V85">
+        <v>0.3</v>
+      </c>
+      <c r="W85">
+        <v>0.03745</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>4.218841624539181</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1053377441829748</v>
+      </c>
+      <c r="C86">
+        <v>1.600623945972954</v>
+      </c>
+      <c r="D86">
+        <v>4.187823945972954</v>
+      </c>
+      <c r="E86">
+        <v>2.5872</v>
+      </c>
+      <c r="F86">
+        <v>2.5872</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>3.08</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.68</v>
+      </c>
+      <c r="K86">
+        <v>1.103</v>
+      </c>
+      <c r="L86">
+        <v>0.577</v>
+      </c>
+      <c r="M86">
+        <v>0.1384152</v>
+      </c>
+      <c r="N86">
+        <v>0.4385847999999999</v>
+      </c>
+      <c r="O86">
+        <v>0.13157544</v>
+      </c>
+      <c r="P86">
+        <v>0.30700936</v>
+      </c>
+      <c r="Q86">
+        <v>1.41000936</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4617484011435924</v>
+      </c>
+      <c r="T86">
+        <v>3.344904924462722</v>
+      </c>
+      <c r="U86">
+        <v>0.0535</v>
+      </c>
+      <c r="V86">
+        <v>0.3</v>
+      </c>
+      <c r="W86">
+        <v>0.03745</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>4.168617319485143</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.105052833444273</v>
+      </c>
+      <c r="C87">
+        <v>1.587833077839046</v>
+      </c>
+      <c r="D87">
+        <v>4.205833077839046</v>
+      </c>
+      <c r="E87">
+        <v>2.618</v>
+      </c>
+      <c r="F87">
+        <v>2.618</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>3.08</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.68</v>
+      </c>
+      <c r="K87">
+        <v>1.103</v>
+      </c>
+      <c r="L87">
+        <v>0.577</v>
+      </c>
+      <c r="M87">
+        <v>0.140063</v>
+      </c>
+      <c r="N87">
+        <v>0.436937</v>
+      </c>
+      <c r="O87">
+        <v>0.1310811</v>
+      </c>
+      <c r="P87">
+        <v>0.3058559</v>
+      </c>
+      <c r="Q87">
+        <v>1.4088559</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4881355562951534</v>
+      </c>
+      <c r="T87">
+        <v>3.553588832406029</v>
+      </c>
+      <c r="U87">
+        <v>0.0535</v>
+      </c>
+      <c r="V87">
+        <v>0.3</v>
+      </c>
+      <c r="W87">
+        <v>0.03745</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>4.119574762785318</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1047679227055713</v>
+      </c>
+      <c r="C88">
+        <v>1.575197770009385</v>
+      </c>
+      <c r="D88">
+        <v>4.223997770009385</v>
+      </c>
+      <c r="E88">
+        <v>2.6488</v>
+      </c>
+      <c r="F88">
+        <v>2.6488</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>3.08</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.68</v>
+      </c>
+      <c r="K88">
+        <v>1.103</v>
+      </c>
+      <c r="L88">
+        <v>0.577</v>
+      </c>
+      <c r="M88">
+        <v>0.1417108</v>
+      </c>
+      <c r="N88">
+        <v>0.4352891999999999</v>
+      </c>
+      <c r="O88">
+        <v>0.13058676</v>
+      </c>
+      <c r="P88">
+        <v>0.30470244</v>
+      </c>
+      <c r="Q88">
+        <v>1.40770244</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5182923050397946</v>
+      </c>
+      <c r="T88">
+        <v>3.79208472719838</v>
+      </c>
+      <c r="U88">
+        <v>0.0535</v>
+      </c>
+      <c r="V88">
+        <v>0.3</v>
+      </c>
+      <c r="W88">
+        <v>0.03745</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>4.071672730659907</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1044830119668695</v>
+      </c>
+      <c r="C89">
+        <v>1.562720046788273</v>
+      </c>
+      <c r="D89">
+        <v>4.242320046788273</v>
+      </c>
+      <c r="E89">
+        <v>2.6796</v>
+      </c>
+      <c r="F89">
+        <v>2.6796</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>3.08</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.68</v>
+      </c>
+      <c r="K89">
+        <v>1.103</v>
+      </c>
+      <c r="L89">
+        <v>0.577</v>
+      </c>
+      <c r="M89">
+        <v>0.1433586</v>
+      </c>
+      <c r="N89">
+        <v>0.4336414</v>
+      </c>
+      <c r="O89">
+        <v>0.13009242</v>
+      </c>
+      <c r="P89">
+        <v>0.30354898</v>
+      </c>
+      <c r="Q89">
+        <v>1.40654898</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5530885535913037</v>
+      </c>
+      <c r="T89">
+        <v>4.067272298112631</v>
+      </c>
+      <c r="U89">
+        <v>0.0535</v>
+      </c>
+      <c r="V89">
+        <v>0.3</v>
+      </c>
+      <c r="W89">
+        <v>0.03745</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>4.024871894675311</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1058613012281677</v>
+      </c>
+      <c r="C90">
+        <v>1.444729013265314</v>
+      </c>
+      <c r="D90">
+        <v>4.155129013265314</v>
+      </c>
+      <c r="E90">
+        <v>2.7104</v>
+      </c>
+      <c r="F90">
+        <v>2.7104</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>3.08</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.68</v>
+      </c>
+      <c r="K90">
+        <v>1.103</v>
+      </c>
+      <c r="L90">
+        <v>0.577</v>
+      </c>
+      <c r="M90">
+        <v>0.15232448</v>
+      </c>
+      <c r="N90">
+        <v>0.42467552</v>
+      </c>
+      <c r="O90">
+        <v>0.127402656</v>
+      </c>
+      <c r="P90">
+        <v>0.297272864</v>
+      </c>
+      <c r="Q90">
+        <v>1.400272864</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5936841769013976</v>
+      </c>
+      <c r="T90">
+        <v>4.388324464179258</v>
+      </c>
+      <c r="U90">
+        <v>0.0562</v>
+      </c>
+      <c r="V90">
+        <v>0.3</v>
+      </c>
+      <c r="W90">
+        <v>0.03934</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.78796632031831</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1055952904894659</v>
+      </c>
+      <c r="C91">
+        <v>1.4304767208974</v>
+      </c>
+      <c r="D91">
+        <v>4.1716767208974</v>
+      </c>
+      <c r="E91">
+        <v>2.7412</v>
+      </c>
+      <c r="F91">
+        <v>2.7412</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>3.08</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.68</v>
+      </c>
+      <c r="K91">
+        <v>1.103</v>
+      </c>
+      <c r="L91">
+        <v>0.577</v>
+      </c>
+      <c r="M91">
+        <v>0.15405544</v>
+      </c>
+      <c r="N91">
+        <v>0.4229445599999999</v>
+      </c>
+      <c r="O91">
+        <v>0.126883368</v>
+      </c>
+      <c r="P91">
+        <v>0.2960611919999999</v>
+      </c>
+      <c r="Q91">
+        <v>1.399061192</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6416608226315086</v>
+      </c>
+      <c r="T91">
+        <v>4.767749751348908</v>
+      </c>
+      <c r="U91">
+        <v>0.0562</v>
+      </c>
+      <c r="V91">
+        <v>0.3</v>
+      </c>
+      <c r="W91">
+        <v>0.03934</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>3.74540490098889</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1053292797507642</v>
+      </c>
+      <c r="C92">
+        <v>1.416356757270979</v>
+      </c>
+      <c r="D92">
+        <v>4.188356757270979</v>
+      </c>
+      <c r="E92">
+        <v>2.772</v>
+      </c>
+      <c r="F92">
+        <v>2.772</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>3.08</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.68</v>
+      </c>
+      <c r="K92">
+        <v>1.103</v>
+      </c>
+      <c r="L92">
+        <v>0.577</v>
+      </c>
+      <c r="M92">
+        <v>0.1557864</v>
+      </c>
+      <c r="N92">
+        <v>0.4212136</v>
+      </c>
+      <c r="O92">
+        <v>0.12636408</v>
+      </c>
+      <c r="P92">
+        <v>0.29484952</v>
+      </c>
+      <c r="Q92">
+        <v>1.39784952</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6992327975076418</v>
+      </c>
+      <c r="T92">
+        <v>5.223060095952487</v>
+      </c>
+      <c r="U92">
+        <v>0.0562</v>
+      </c>
+      <c r="V92">
+        <v>0.3</v>
+      </c>
+      <c r="W92">
+        <v>0.03934</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>3.703789290977903</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1050632690120624</v>
+      </c>
+      <c r="C93">
+        <v>1.402370716068355</v>
+      </c>
+      <c r="D93">
+        <v>4.205170716068355</v>
+      </c>
+      <c r="E93">
+        <v>2.8028</v>
+      </c>
+      <c r="F93">
+        <v>2.8028</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>3.08</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.68</v>
+      </c>
+      <c r="K93">
+        <v>1.103</v>
+      </c>
+      <c r="L93">
+        <v>0.577</v>
+      </c>
+      <c r="M93">
+        <v>0.15751736</v>
+      </c>
+      <c r="N93">
+        <v>0.41948264</v>
+      </c>
+      <c r="O93">
+        <v>0.125844792</v>
+      </c>
+      <c r="P93">
+        <v>0.293637848</v>
+      </c>
+      <c r="Q93">
+        <v>1.396637848</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7695985445784712</v>
+      </c>
+      <c r="T93">
+        <v>5.77955051713464</v>
+      </c>
+      <c r="U93">
+        <v>0.0562</v>
+      </c>
+      <c r="V93">
+        <v>0.3</v>
+      </c>
+      <c r="W93">
+        <v>0.03934</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>3.663088309758365</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1047972582733606</v>
+      </c>
+      <c r="C94">
+        <v>1.388520216666016</v>
+      </c>
+      <c r="D94">
+        <v>4.222120216666016</v>
+      </c>
+      <c r="E94">
+        <v>2.8336</v>
+      </c>
+      <c r="F94">
+        <v>2.8336</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>3.08</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.68</v>
+      </c>
+      <c r="K94">
+        <v>1.103</v>
+      </c>
+      <c r="L94">
+        <v>0.577</v>
+      </c>
+      <c r="M94">
+        <v>0.15924832</v>
+      </c>
+      <c r="N94">
+        <v>0.41775168</v>
+      </c>
+      <c r="O94">
+        <v>0.125325504</v>
+      </c>
+      <c r="P94">
+        <v>0.292426176</v>
+      </c>
+      <c r="Q94">
+        <v>1.395426176</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8575557284170083</v>
+      </c>
+      <c r="T94">
+        <v>6.475163543612331</v>
+      </c>
+      <c r="U94">
+        <v>0.0562</v>
+      </c>
+      <c r="V94">
+        <v>0.3</v>
+      </c>
+      <c r="W94">
+        <v>0.03934</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>3.623272132478383</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1045312475346589</v>
+      </c>
+      <c r="C95">
+        <v>1.374806904654569</v>
+      </c>
+      <c r="D95">
+        <v>4.239206904654569</v>
+      </c>
+      <c r="E95">
+        <v>2.8644</v>
+      </c>
+      <c r="F95">
+        <v>2.8644</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>3.08</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.68</v>
+      </c>
+      <c r="K95">
+        <v>1.103</v>
+      </c>
+      <c r="L95">
+        <v>0.577</v>
+      </c>
+      <c r="M95">
+        <v>0.16097928</v>
+      </c>
+      <c r="N95">
+        <v>0.41602072</v>
+      </c>
+      <c r="O95">
+        <v>0.124806216</v>
+      </c>
+      <c r="P95">
+        <v>0.291214504</v>
+      </c>
+      <c r="Q95">
+        <v>1.394214504</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9706435362094128</v>
+      </c>
+      <c r="T95">
+        <v>7.369523149083649</v>
+      </c>
+      <c r="U95">
+        <v>0.0562</v>
+      </c>
+      <c r="V95">
+        <v>0.3</v>
+      </c>
+      <c r="W95">
+        <v>0.03934</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>3.58431221707539</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1042652367959571</v>
+      </c>
+      <c r="C96">
+        <v>1.361232452371314</v>
+      </c>
+      <c r="D96">
+        <v>4.256432452371315</v>
+      </c>
+      <c r="E96">
+        <v>2.8952</v>
+      </c>
+      <c r="F96">
+        <v>2.8952</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>3.08</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.68</v>
+      </c>
+      <c r="K96">
+        <v>1.103</v>
+      </c>
+      <c r="L96">
+        <v>0.577</v>
+      </c>
+      <c r="M96">
+        <v>0.16271024</v>
+      </c>
+      <c r="N96">
+        <v>0.41428976</v>
+      </c>
+      <c r="O96">
+        <v>0.124286928</v>
+      </c>
+      <c r="P96">
+        <v>0.290002832</v>
+      </c>
+      <c r="Q96">
+        <v>1.393002832</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.121427279932619</v>
+      </c>
+      <c r="T96">
+        <v>8.562002623045407</v>
+      </c>
+      <c r="U96">
+        <v>0.0562</v>
+      </c>
+      <c r="V96">
+        <v>0.3</v>
+      </c>
+      <c r="W96">
+        <v>0.03934</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>3.546181236042672</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1039992260572553</v>
+      </c>
+      <c r="C97">
+        <v>1.347798559445886</v>
+      </c>
+      <c r="D97">
+        <v>4.273798559445886</v>
+      </c>
+      <c r="E97">
+        <v>2.926</v>
+      </c>
+      <c r="F97">
+        <v>2.926</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>3.08</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.68</v>
+      </c>
+      <c r="K97">
+        <v>1.103</v>
+      </c>
+      <c r="L97">
+        <v>0.577</v>
+      </c>
+      <c r="M97">
+        <v>0.1644412</v>
+      </c>
+      <c r="N97">
+        <v>0.4125587999999999</v>
+      </c>
+      <c r="O97">
+        <v>0.12376764</v>
+      </c>
+      <c r="P97">
+        <v>0.2887911599999999</v>
+      </c>
+      <c r="Q97">
+        <v>1.39179116</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.332524521145108</v>
+      </c>
+      <c r="T97">
+        <v>10.23147388659187</v>
+      </c>
+      <c r="U97">
+        <v>0.0562</v>
+      </c>
+      <c r="V97">
+        <v>0.3</v>
+      </c>
+      <c r="W97">
+        <v>0.03934</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>3.508853012505381</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1068916153185535</v>
+      </c>
+      <c r="C98">
+        <v>1.135456544317265</v>
+      </c>
+      <c r="D98">
+        <v>4.092256544317265</v>
+      </c>
+      <c r="E98">
+        <v>2.9568</v>
+      </c>
+      <c r="F98">
+        <v>2.9568</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>3.08</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.68</v>
+      </c>
+      <c r="K98">
+        <v>1.103</v>
+      </c>
+      <c r="L98">
+        <v>0.577</v>
+      </c>
+      <c r="M98">
+        <v>0.18006912</v>
+      </c>
+      <c r="N98">
+        <v>0.39693088</v>
+      </c>
+      <c r="O98">
+        <v>0.119079264</v>
+      </c>
+      <c r="P98">
+        <v>0.277851616</v>
+      </c>
+      <c r="Q98">
+        <v>1.380851616</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.649170382963837</v>
+      </c>
+      <c r="T98">
+        <v>12.73568078191153</v>
+      </c>
+      <c r="U98">
+        <v>0.0609</v>
+      </c>
+      <c r="V98">
+        <v>0.3</v>
+      </c>
+      <c r="W98">
+        <v>0.04263</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>3.204325094719183</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1066585045798518</v>
+      </c>
+      <c r="C99">
+        <v>1.118714457203929</v>
+      </c>
+      <c r="D99">
+        <v>4.106314457203929</v>
+      </c>
+      <c r="E99">
+        <v>2.9876</v>
+      </c>
+      <c r="F99">
+        <v>2.9876</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>3.08</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.68</v>
+      </c>
+      <c r="K99">
+        <v>1.103</v>
+      </c>
+      <c r="L99">
+        <v>0.577</v>
+      </c>
+      <c r="M99">
+        <v>0.18194484</v>
+      </c>
+      <c r="N99">
+        <v>0.39505516</v>
+      </c>
+      <c r="O99">
+        <v>0.118516548</v>
+      </c>
+      <c r="P99">
+        <v>0.276538612</v>
+      </c>
+      <c r="Q99">
+        <v>1.379538612</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.176913485995058</v>
+      </c>
+      <c r="T99">
+        <v>16.90935894077767</v>
+      </c>
+      <c r="U99">
+        <v>0.0609</v>
+      </c>
+      <c r="V99">
+        <v>0.3</v>
+      </c>
+      <c r="W99">
+        <v>0.04263</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>3.171290815392181</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.10642539384115</v>
+      </c>
+      <c r="C100">
+        <v>1.102069287839135</v>
+      </c>
+      <c r="D100">
+        <v>4.120469287839136</v>
+      </c>
+      <c r="E100">
+        <v>3.0184</v>
+      </c>
+      <c r="F100">
+        <v>3.0184</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>3.08</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.68</v>
+      </c>
+      <c r="K100">
+        <v>1.103</v>
+      </c>
+      <c r="L100">
+        <v>0.577</v>
+      </c>
+      <c r="M100">
+        <v>0.18382056</v>
+      </c>
+      <c r="N100">
+        <v>0.3931794399999999</v>
+      </c>
+      <c r="O100">
+        <v>0.117953832</v>
+      </c>
+      <c r="P100">
+        <v>0.275225608</v>
+      </c>
+      <c r="Q100">
+        <v>1.378225608</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.232399692057498</v>
+      </c>
+      <c r="T100">
+        <v>25.25671525850995</v>
+      </c>
+      <c r="U100">
+        <v>0.0609</v>
+      </c>
+      <c r="V100">
+        <v>0.3</v>
+      </c>
+      <c r="W100">
+        <v>0.04263</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>3.138930705031036</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1061922831024482</v>
+      </c>
+      <c r="C101">
+        <v>1.085522041941945</v>
+      </c>
+      <c r="D101">
+        <v>4.134722041941945</v>
+      </c>
+      <c r="E101">
+        <v>3.0492</v>
+      </c>
+      <c r="F101">
+        <v>3.0492</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>3.08</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.68</v>
+      </c>
+      <c r="K101">
+        <v>1.103</v>
+      </c>
+      <c r="L101">
+        <v>0.577</v>
+      </c>
+      <c r="M101">
+        <v>0.18569628</v>
+      </c>
+      <c r="N101">
+        <v>0.39130372</v>
+      </c>
+      <c r="O101">
+        <v>0.117391116</v>
+      </c>
+      <c r="P101">
+        <v>0.2739126039999999</v>
+      </c>
+      <c r="Q101">
+        <v>1.376912604</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.398858310244818</v>
+      </c>
+      <c r="T101">
+        <v>50.29878421170677</v>
+      </c>
+      <c r="U101">
+        <v>0.0609</v>
+      </c>
+      <c r="V101">
+        <v>0.3</v>
+      </c>
+      <c r="W101">
+        <v>0.04263</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>3.107224334273147</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
